--- a/Database/260506_Datenbankdefinition_Hochbau.xlsx
+++ b/Database/260506_Datenbankdefinition_Hochbau.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodelan\PycharmProjects\StustainabilityDrivenStructuralDesign\Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodelan\PycharmProjects\StustainabilityDrivenStructuralDesign\260513_Betonartikel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A73C98-0ADD-464B-88E3-7692537D075C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA2977C-3305-495C-98C4-E5781DD7ECD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
@@ -6596,7 +6596,7 @@
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>75557</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>37463</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7039,7 +7039,19 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{47D9B8EF-9A77-4F45-A199-649B0FE0D597}" name="Table24" displayName="Table24" ref="A1:AL265" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A1:AL265" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}"/>
+  <autoFilter ref="A1:AL265" xr:uid="{690E7B34-75E3-43BA-8CDD-44A4EFCCEFD5}">
+    <filterColumn colId="13">
+      <filters>
+        <filter val="ready_mixed_concrete"/>
+        <filter val="Steel_reinforcing_bar"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="34">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="38">
     <tableColumn id="9" xr3:uid="{E6171A79-2142-45AE-B13A-B85672F5EDBD}" name="ID" dataDxfId="54"/>
     <tableColumn id="28" xr3:uid="{68E92EDC-8025-4BF4-9A42-9CF0006FBF63}" name="Copy for strength" dataDxfId="53"/>
@@ -7089,8 +7101,12 @@
     </tableColumn>
     <tableColumn id="38" xr3:uid="{9D6F0D53-6C6D-475E-BF1D-F0D5C13DE2AB}" name="MIN_MAX" dataDxfId="20">
       <calculatedColumnFormula array="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V2=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P2))),1,
-IF(V2=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P2))),1,0)),0)</calculatedColumnFormula>
+IF(
+OR(
+V2=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P2)*($AH$2:$AH$282&lt;&gt;0))),
+V2=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P2)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P2)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{632F69D0-7DBB-46E2-96F6-C24109AFEFA9}" name="Cost" dataDxfId="19"/>
     <tableColumn id="24" xr3:uid="{814B05BF-1F84-451C-BBB8-00EC879AE2A7}" name="Anmerkung I" dataDxfId="18"/>
@@ -7956,7 +7972,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="2" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="167" t="s">
         <v>332</v>
       </c>
@@ -8048,15 +8064,19 @@
       </c>
       <c r="AI2" s="178" cm="1">
         <f t="array" aca="1" ref="AI2" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V2=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P2))),1,
-IF(V2=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P2))),1,0)),0)</f>
+IF(
+OR(
+V2=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P2)*($AH$2:$AH$282&lt;&gt;0))),
+V2=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P2)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P2)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ2" s="180"/>
       <c r="AK2" s="5"/>
       <c r="AL2" s="5"/>
     </row>
-    <row r="3" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" s="167" t="s">
         <v>333</v>
       </c>
@@ -8148,15 +8168,19 @@
       </c>
       <c r="AI3" s="178" cm="1">
         <f t="array" aca="1" ref="AI3" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V3=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P3))),1,
-IF(V3=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P3))),1,0)),0)</f>
+IF(
+OR(
+V3=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P3)*($AH$2:$AH$282&lt;&gt;0))),
+V3=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P3)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P3)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ3" s="180"/>
       <c r="AK3" s="5"/>
       <c r="AL3" s="5"/>
     </row>
-    <row r="4" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" s="167" t="s">
         <v>334</v>
       </c>
@@ -8248,15 +8272,19 @@
       </c>
       <c r="AI4" s="178" cm="1">
         <f t="array" aca="1" ref="AI4" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V4=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P4))),1,
-IF(V4=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P4))),1,0)),0)</f>
+IF(
+OR(
+V4=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P4)*($AH$2:$AH$282&lt;&gt;0))),
+V4=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P4)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P4)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ4" s="180"/>
       <c r="AK4" s="5"/>
       <c r="AL4" s="5"/>
     </row>
-    <row r="5" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" s="167" t="s">
         <v>335</v>
       </c>
@@ -8348,15 +8376,19 @@
       </c>
       <c r="AI5" s="178" cm="1">
         <f t="array" aca="1" ref="AI5" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V5=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P5))),1,
-IF(V5=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P5))),1,0)),0)</f>
+IF(
+OR(
+V5=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P5)*($AH$2:$AH$282&lt;&gt;0))),
+V5=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P5)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P5)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ5" s="180"/>
       <c r="AK5" s="5"/>
       <c r="AL5" s="5"/>
     </row>
-    <row r="6" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="167" t="s">
         <v>336</v>
       </c>
@@ -8448,15 +8480,19 @@
       </c>
       <c r="AI6" s="178" cm="1">
         <f t="array" aca="1" ref="AI6" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V6=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P6))),1,
-IF(V6=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P6))),1,0)),0)</f>
+IF(
+OR(
+V6=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P6)*($AH$2:$AH$282&lt;&gt;0))),
+V6=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P6)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P6)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ6" s="180"/>
       <c r="AK6" s="5"/>
       <c r="AL6" s="5"/>
     </row>
-    <row r="7" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="167" t="s">
         <v>337</v>
       </c>
@@ -8537,15 +8573,19 @@
       </c>
       <c r="AI7" s="178" cm="1">
         <f t="array" aca="1" ref="AI7" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V7=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P7))),1,
-IF(V7=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P7))),1,0)),0)</f>
+IF(
+OR(
+V7=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P7)*($AH$2:$AH$282&lt;&gt;0))),
+V7=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P7)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P7)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ7" s="180"/>
       <c r="AK7" s="5"/>
       <c r="AL7" s="5"/>
     </row>
-    <row r="8" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" s="167" t="s">
         <v>338</v>
       </c>
@@ -8626,15 +8666,19 @@
       </c>
       <c r="AI8" s="178" cm="1">
         <f t="array" aca="1" ref="AI8" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V8=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P8))),1,
-IF(V8=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P8))),1,0)),0)</f>
+IF(
+OR(
+V8=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P8)*($AH$2:$AH$282&lt;&gt;0))),
+V8=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P8)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P8)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ8" s="180"/>
       <c r="AK8" s="5"/>
       <c r="AL8" s="5"/>
     </row>
-    <row r="9" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="167" t="s">
         <v>339</v>
       </c>
@@ -8715,15 +8759,19 @@
       </c>
       <c r="AI9" s="178" cm="1">
         <f t="array" aca="1" ref="AI9" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V9=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P9))),1,
-IF(V9=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P9))),1,0)),0)</f>
+IF(
+OR(
+V9=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P9)*($AH$2:$AH$282&lt;&gt;0))),
+V9=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P9)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P9)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ9" s="180"/>
       <c r="AK9" s="5"/>
       <c r="AL9" s="5"/>
     </row>
-    <row r="10" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="167" t="s">
         <v>340</v>
       </c>
@@ -8804,15 +8852,19 @@
       </c>
       <c r="AI10" s="178" cm="1">
         <f t="array" aca="1" ref="AI10" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V10=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P10))),1,
-IF(V10=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P10))),1,0)),0)</f>
+IF(
+OR(
+V10=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P10)*($AH$2:$AH$282&lt;&gt;0))),
+V10=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P10)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P10)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ10" s="180"/>
       <c r="AK10" s="5"/>
       <c r="AL10" s="5"/>
     </row>
-    <row r="11" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="167" t="s">
         <v>341</v>
       </c>
@@ -8893,15 +8945,19 @@
       </c>
       <c r="AI11" s="178" cm="1">
         <f t="array" aca="1" ref="AI11" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V11=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P11))),1,
-IF(V11=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P11))),1,0)),0)</f>
+IF(
+OR(
+V11=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P11)*($AH$2:$AH$282&lt;&gt;0))),
+V11=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P11)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P11)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ11" s="180"/>
       <c r="AK11" s="5"/>
       <c r="AL11" s="5"/>
     </row>
-    <row r="12" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="167" t="s">
         <v>342</v>
       </c>
@@ -8993,15 +9049,19 @@
       </c>
       <c r="AI12" s="178" cm="1">
         <f t="array" aca="1" ref="AI12" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V12=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P12))),1,
-IF(V12=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P12))),1,0)),0)</f>
+IF(
+OR(
+V12=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P12)*($AH$2:$AH$282&lt;&gt;0))),
+V12=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P12)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P12)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ12" s="180"/>
       <c r="AK12" s="5"/>
       <c r="AL12" s="5"/>
     </row>
-    <row r="13" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" s="182" t="s">
         <v>343</v>
       </c>
@@ -9096,15 +9156,19 @@
       </c>
       <c r="AI13" s="178" cm="1">
         <f t="array" aca="1" ref="AI13" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V13=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P13))),1,
-IF(V13=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P13))),1,0)),0)</f>
+IF(
+OR(
+V13=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P13)*($AH$2:$AH$282&lt;&gt;0))),
+V13=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P13)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P13)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ13" s="180"/>
       <c r="AK13" s="12"/>
       <c r="AL13" s="12"/>
     </row>
-    <row r="14" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="182" t="s">
         <v>344</v>
       </c>
@@ -9199,15 +9263,19 @@
       </c>
       <c r="AI14" s="178" cm="1">
         <f t="array" aca="1" ref="AI14" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V14=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P14))),1,
-IF(V14=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P14))),1,0)),0)</f>
+IF(
+OR(
+V14=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P14)*($AH$2:$AH$282&lt;&gt;0))),
+V14=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P14)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P14)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ14" s="180"/>
       <c r="AK14" s="12"/>
       <c r="AL14" s="12"/>
     </row>
-    <row r="15" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="182" t="s">
         <v>345</v>
       </c>
@@ -9302,15 +9370,19 @@
       </c>
       <c r="AI15" s="178" cm="1">
         <f t="array" aca="1" ref="AI15" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V15=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P15))),1,
-IF(V15=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P15))),1,0)),0)</f>
+IF(
+OR(
+V15=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P15)*($AH$2:$AH$282&lt;&gt;0))),
+V15=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P15)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P15)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ15" s="180"/>
       <c r="AK15" s="12"/>
       <c r="AL15" s="12"/>
     </row>
-    <row r="16" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" s="182" t="s">
         <v>346</v>
       </c>
@@ -9405,15 +9477,19 @@
       </c>
       <c r="AI16" s="178" cm="1">
         <f t="array" aca="1" ref="AI16" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V16=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P16))),1,
-IF(V16=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P16))),1,0)),0)</f>
+IF(
+OR(
+V16=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P16)*($AH$2:$AH$282&lt;&gt;0))),
+V16=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P16)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P16)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ16" s="180"/>
       <c r="AK16" s="12"/>
       <c r="AL16" s="12"/>
     </row>
-    <row r="17" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="182" t="s">
         <v>347</v>
       </c>
@@ -9508,15 +9584,19 @@
       </c>
       <c r="AI17" s="178" cm="1">
         <f t="array" aca="1" ref="AI17" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V17=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P17))),1,
-IF(V17=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P17))),1,0)),0)</f>
+IF(
+OR(
+V17=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P17)*($AH$2:$AH$282&lt;&gt;0))),
+V17=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P17)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P17)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ17" s="180"/>
       <c r="AK17" s="12"/>
       <c r="AL17" s="12"/>
     </row>
-    <row r="18" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="182" t="s">
         <v>348</v>
       </c>
@@ -9611,15 +9691,19 @@
       </c>
       <c r="AI18" s="178" cm="1">
         <f t="array" aca="1" ref="AI18" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V18=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P18))),1,
-IF(V18=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P18))),1,0)),0)</f>
+IF(
+OR(
+V18=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P18)*($AH$2:$AH$282&lt;&gt;0))),
+V18=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P18)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P18)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ18" s="180"/>
       <c r="AK18" s="12"/>
       <c r="AL18" s="12"/>
     </row>
-    <row r="19" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="182" t="s">
         <v>349</v>
       </c>
@@ -9714,15 +9798,19 @@
       </c>
       <c r="AI19" s="178" cm="1">
         <f t="array" aca="1" ref="AI19" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V19=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P19))),1,
-IF(V19=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P19))),1,0)),0)</f>
+IF(
+OR(
+V19=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P19)*($AH$2:$AH$282&lt;&gt;0))),
+V19=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P19)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P19)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ19" s="180"/>
       <c r="AK19" s="12"/>
       <c r="AL19" s="12"/>
     </row>
-    <row r="20" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="182" t="s">
         <v>350</v>
       </c>
@@ -9817,15 +9905,19 @@
       </c>
       <c r="AI20" s="178" cm="1">
         <f t="array" aca="1" ref="AI20" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V20=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P20))),1,
-IF(V20=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P20))),1,0)),0)</f>
+IF(
+OR(
+V20=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P20)*($AH$2:$AH$282&lt;&gt;0))),
+V20=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P20)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P20)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ20" s="180"/>
       <c r="AK20" s="12"/>
       <c r="AL20" s="12"/>
     </row>
-    <row r="21" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="182" t="s">
         <v>351</v>
       </c>
@@ -9920,15 +10012,19 @@
       </c>
       <c r="AI21" s="178" cm="1">
         <f t="array" aca="1" ref="AI21" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V21=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P21))),1,
-IF(V21=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P21))),1,0)),0)</f>
+IF(
+OR(
+V21=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P21)*($AH$2:$AH$282&lt;&gt;0))),
+V21=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P21)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P21)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ21" s="180"/>
       <c r="AK21" s="12"/>
       <c r="AL21" s="12"/>
     </row>
-    <row r="22" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="182" t="s">
         <v>352</v>
       </c>
@@ -10023,15 +10119,19 @@
       </c>
       <c r="AI22" s="178" cm="1">
         <f t="array" aca="1" ref="AI22" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V22=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P22))),1,
-IF(V22=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P22))),1,0)),0)</f>
+IF(
+OR(
+V22=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P22)*($AH$2:$AH$282&lt;&gt;0))),
+V22=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P22)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P22)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ22" s="180"/>
       <c r="AK22" s="12"/>
       <c r="AL22" s="12"/>
     </row>
-    <row r="23" spans="1:38" s="13" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:38" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="182" t="s">
         <v>353</v>
       </c>
@@ -10126,8 +10226,12 @@
       </c>
       <c r="AI23" s="178" cm="1">
         <f t="array" aca="1" ref="AI23" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V23=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P23))),1,
-IF(V23=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P23))),1,0)),0)</f>
+IF(
+OR(
+V23=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P23)*($AH$2:$AH$282&lt;&gt;0))),
+V23=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P23)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P23)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ23" s="180"/>
@@ -10229,15 +10333,19 @@
       </c>
       <c r="AI24" s="178" cm="1">
         <f t="array" aca="1" ref="AI24" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V24=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P24))),1,
-IF(V24=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P24))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V24=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P24)*($AH$2:$AH$282&lt;&gt;0))),
+V24=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P24)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P24)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ24" s="180"/>
       <c r="AK24" s="2"/>
       <c r="AL24" s="2"/>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="199" t="s">
         <v>195</v>
       </c>
@@ -10332,15 +10440,19 @@
       </c>
       <c r="AI25" s="178" cm="1">
         <f t="array" aca="1" ref="AI25" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V25=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P25))),1,
-IF(V25=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P25))),1,0)),0)</f>
+IF(
+OR(
+V25=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P25)*($AH$2:$AH$282&lt;&gt;0))),
+V25=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P25)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P25)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ25" s="180"/>
       <c r="AK25" s="2"/>
       <c r="AL25" s="2"/>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="199" t="s">
         <v>196</v>
       </c>
@@ -10435,15 +10547,19 @@
       </c>
       <c r="AI26" s="178" cm="1">
         <f t="array" aca="1" ref="AI26" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V26=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P26))),1,
-IF(V26=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P26))),1,0)),0)</f>
+IF(
+OR(
+V26=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P26)*($AH$2:$AH$282&lt;&gt;0))),
+V26=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P26)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P26)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ26" s="180"/>
       <c r="AK26" s="2"/>
       <c r="AL26" s="2"/>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="199" t="s">
         <v>197</v>
       </c>
@@ -10538,15 +10654,19 @@
       </c>
       <c r="AI27" s="178" cm="1">
         <f t="array" aca="1" ref="AI27" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V27=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P27))),1,
-IF(V27=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P27))),1,0)),0)</f>
+IF(
+OR(
+V27=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P27)*($AH$2:$AH$282&lt;&gt;0))),
+V27=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P27)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P27)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ27" s="180"/>
       <c r="AK27" s="2"/>
       <c r="AL27" s="2"/>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" s="199" t="s">
         <v>198</v>
       </c>
@@ -10641,15 +10761,19 @@
       </c>
       <c r="AI28" s="178" cm="1">
         <f t="array" aca="1" ref="AI28" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V28=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P28))),1,
-IF(V28=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P28))),1,0)),0)</f>
+IF(
+OR(
+V28=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P28)*($AH$2:$AH$282&lt;&gt;0))),
+V28=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P28)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P28)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ28" s="180"/>
       <c r="AK28" s="2"/>
       <c r="AL28" s="2"/>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="199" t="s">
         <v>199</v>
       </c>
@@ -10744,15 +10868,19 @@
       </c>
       <c r="AI29" s="178" cm="1">
         <f t="array" aca="1" ref="AI29" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V29=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P29))),1,
-IF(V29=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P29))),1,0)),0)</f>
+IF(
+OR(
+V29=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P29)*($AH$2:$AH$282&lt;&gt;0))),
+V29=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P29)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P29)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ29" s="180"/>
       <c r="AK29" s="2"/>
       <c r="AL29" s="2"/>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="199" t="s">
         <v>200</v>
       </c>
@@ -10847,15 +10975,19 @@
       </c>
       <c r="AI30" s="178" cm="1">
         <f t="array" aca="1" ref="AI30" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V30=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P30))),1,
-IF(V30=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P30))),1,0)),0)</f>
+IF(
+OR(
+V30=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P30)*($AH$2:$AH$282&lt;&gt;0))),
+V30=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P30)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P30)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ30" s="180"/>
       <c r="AK30" s="2"/>
       <c r="AL30" s="2"/>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="199" t="s">
         <v>626</v>
       </c>
@@ -10962,8 +11094,12 @@
       </c>
       <c r="AI31" s="178" cm="1">
         <f t="array" aca="1" ref="AI31" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V31=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P31))),1,
-IF(V31=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P31))),1,0)),0)</f>
+IF(
+OR(
+V31=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P31)*($AH$2:$AH$282&lt;&gt;0))),
+V31=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P31)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P31)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ31" s="180"/>
@@ -11077,15 +11213,19 @@
       </c>
       <c r="AI32" s="178" cm="1">
         <f t="array" aca="1" ref="AI32" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V32=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P32))),1,
-IF(V32=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P32))),1,0)),0)</f>
+IF(
+OR(
+V32=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P32)*($AH$2:$AH$282&lt;&gt;0))),
+V32=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P32)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P32)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ32" s="180"/>
       <c r="AK32" s="118"/>
       <c r="AL32" s="2"/>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="199" t="s">
         <v>628</v>
       </c>
@@ -11192,8 +11332,12 @@
       </c>
       <c r="AI33" s="178" cm="1">
         <f t="array" aca="1" ref="AI33" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V33=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P33))),1,
-IF(V33=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P33))),1,0)),0)</f>
+IF(
+OR(
+V33=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P33)*($AH$2:$AH$282&lt;&gt;0))),
+V33=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P33)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P33)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ33" s="180"/>
@@ -11307,8 +11451,12 @@
       </c>
       <c r="AI34" s="178" cm="1">
         <f t="array" aca="1" ref="AI34" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V34=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P34))),1,
-IF(V34=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P34))),1,0)),0)</f>
+IF(
+OR(
+V34=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P34)*($AH$2:$AH$282&lt;&gt;0))),
+V34=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P34)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P34)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ34" s="180"/>
@@ -11422,9 +11570,13 @@
       </c>
       <c r="AI35" s="178" cm="1">
         <f t="array" aca="1" ref="AI35" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V35=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P35))),1,
-IF(V35=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P35))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V35=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P35)*($AH$2:$AH$282&lt;&gt;0))),
+V35=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P35)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P35)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ35" s="180"/>
       <c r="AK35" s="118"/>
@@ -11537,15 +11689,19 @@
       </c>
       <c r="AI36" s="178" cm="1">
         <f t="array" aca="1" ref="AI36" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V36=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P36))),1,
-IF(V36=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P36))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V36=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P36)*($AH$2:$AH$282&lt;&gt;0))),
+V36=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P36)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P36)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ36" s="180"/>
       <c r="AK36" s="118"/>
       <c r="AL36" s="2"/>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" s="199" t="s">
         <v>632</v>
       </c>
@@ -11652,15 +11808,19 @@
       </c>
       <c r="AI37" s="178" cm="1">
         <f t="array" aca="1" ref="AI37" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V37=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P37))),1,
-IF(V37=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P37))),1,0)),0)</f>
+IF(
+OR(
+V37=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P37)*($AH$2:$AH$282&lt;&gt;0))),
+V37=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P37)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P37)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ37" s="180"/>
       <c r="AK37" s="118"/>
       <c r="AL37" s="2"/>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" s="199" t="s">
         <v>633</v>
       </c>
@@ -11767,15 +11927,19 @@
       </c>
       <c r="AI38" s="178" cm="1">
         <f t="array" aca="1" ref="AI38" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V38=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P38))),1,
-IF(V38=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P38))),1,0)),0)</f>
+IF(
+OR(
+V38=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P38)*($AH$2:$AH$282&lt;&gt;0))),
+V38=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P38)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P38)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ38" s="180"/>
       <c r="AK38" s="118"/>
       <c r="AL38" s="2"/>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" s="199" t="s">
         <v>634</v>
       </c>
@@ -11882,15 +12046,19 @@
       </c>
       <c r="AI39" s="178" cm="1">
         <f t="array" aca="1" ref="AI39" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V39=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P39))),1,
-IF(V39=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P39))),1,0)),0)</f>
+IF(
+OR(
+V39=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P39)*($AH$2:$AH$282&lt;&gt;0))),
+V39=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P39)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P39)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ39" s="180"/>
       <c r="AK39" s="118"/>
       <c r="AL39" s="2"/>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="199" t="s">
         <v>635</v>
       </c>
@@ -11997,15 +12165,19 @@
       </c>
       <c r="AI40" s="178" cm="1">
         <f t="array" aca="1" ref="AI40" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V40=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P40))),1,
-IF(V40=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P40))),1,0)),0)</f>
+IF(
+OR(
+V40=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P40)*($AH$2:$AH$282&lt;&gt;0))),
+V40=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P40)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P40)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ40" s="180"/>
       <c r="AK40" s="118"/>
       <c r="AL40" s="2"/>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" s="199" t="s">
         <v>636</v>
       </c>
@@ -12112,15 +12284,19 @@
       </c>
       <c r="AI41" s="178" cm="1">
         <f t="array" aca="1" ref="AI41" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V41=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P41))),1,
-IF(V41=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P41))),1,0)),0)</f>
+IF(
+OR(
+V41=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P41)*($AH$2:$AH$282&lt;&gt;0))),
+V41=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P41)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P41)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ41" s="180"/>
       <c r="AK41" s="118"/>
       <c r="AL41" s="2"/>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="199" t="s">
         <v>637</v>
       </c>
@@ -12227,15 +12403,19 @@
       </c>
       <c r="AI42" s="178" cm="1">
         <f t="array" aca="1" ref="AI42" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V42=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P42))),1,
-IF(V42=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P42))),1,0)),0)</f>
+IF(
+OR(
+V42=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P42)*($AH$2:$AH$282&lt;&gt;0))),
+V42=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P42)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P42)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ42" s="180"/>
       <c r="AK42" s="118"/>
       <c r="AL42" s="2"/>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="199" t="s">
         <v>638</v>
       </c>
@@ -12342,15 +12522,19 @@
       </c>
       <c r="AI43" s="178" cm="1">
         <f t="array" aca="1" ref="AI43" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V43=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P43))),1,
-IF(V43=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P43))),1,0)),0)</f>
+IF(
+OR(
+V43=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P43)*($AH$2:$AH$282&lt;&gt;0))),
+V43=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P43)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P43)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ43" s="180"/>
       <c r="AK43" s="118"/>
       <c r="AL43" s="2"/>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" s="199" t="s">
         <v>639</v>
       </c>
@@ -12457,8 +12641,12 @@
       </c>
       <c r="AI44" s="178" cm="1">
         <f t="array" aca="1" ref="AI44" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V44=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P44))),1,
-IF(V44=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P44))),1,0)),0)</f>
+IF(
+OR(
+V44=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P44)*($AH$2:$AH$282&lt;&gt;0))),
+V44=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P44)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P44)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ44" s="180"/>
@@ -12572,15 +12760,19 @@
       </c>
       <c r="AI45" s="178" cm="1">
         <f t="array" aca="1" ref="AI45" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V45=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P45))),1,
-IF(V45=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P45))),1,0)),0)</f>
+IF(
+OR(
+V45=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P45)*($AH$2:$AH$282&lt;&gt;0))),
+V45=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P45)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P45)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ45" s="180"/>
       <c r="AK45" s="2"/>
       <c r="AL45" s="2"/>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" s="199" t="s">
         <v>641</v>
       </c>
@@ -12687,15 +12879,19 @@
       </c>
       <c r="AI46" s="178" cm="1">
         <f t="array" aca="1" ref="AI46" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V46=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P46))),1,
-IF(V46=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P46))),1,0)),0)</f>
+IF(
+OR(
+V46=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P46)*($AH$2:$AH$282&lt;&gt;0))),
+V46=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P46)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P46)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ46" s="180"/>
       <c r="AK46" s="2"/>
       <c r="AL46" s="2"/>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" s="199" t="s">
         <v>642</v>
       </c>
@@ -12802,15 +12998,19 @@
       </c>
       <c r="AI47" s="178" cm="1">
         <f t="array" aca="1" ref="AI47" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V47=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P47))),1,
-IF(V47=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P47))),1,0)),0)</f>
+IF(
+OR(
+V47=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P47)*($AH$2:$AH$282&lt;&gt;0))),
+V47=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P47)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P47)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ47" s="180"/>
       <c r="AK47" s="2"/>
       <c r="AL47" s="2"/>
     </row>
-    <row r="48" spans="1:38" s="154" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:38" s="154" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" s="199" t="s">
         <v>643</v>
       </c>
@@ -12859,15 +13059,19 @@
       </c>
       <c r="AI48" s="178" cm="1">
         <f t="array" aca="1" ref="AI48" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V48=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P48))),1,
-IF(V48=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P48))),1,0)),0)</f>
+IF(
+OR(
+V48=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P48)*($AH$2:$AH$282&lt;&gt;0))),
+V48=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P48)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P48)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ48" s="180"/>
       <c r="AK48" s="153"/>
       <c r="AL48" s="153"/>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" s="199" t="s">
         <v>644</v>
       </c>
@@ -12974,15 +13178,19 @@
       </c>
       <c r="AI49" s="178" cm="1">
         <f t="array" aca="1" ref="AI49" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V49=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P49))),1,
-IF(V49=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P49))),1,0)),0)</f>
+IF(
+OR(
+V49=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P49)*($AH$2:$AH$282&lt;&gt;0))),
+V49=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P49)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P49)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ49" s="180"/>
       <c r="AK49" s="2"/>
       <c r="AL49" s="2"/>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="199" t="s">
         <v>667</v>
       </c>
@@ -13089,15 +13297,19 @@
       </c>
       <c r="AI50" s="178" cm="1">
         <f t="array" aca="1" ref="AI50" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V50=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P50))),1,
-IF(V50=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P50))),1,0)),0)</f>
+IF(
+OR(
+V50=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P50)*($AH$2:$AH$282&lt;&gt;0))),
+V50=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P50)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P50)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ50" s="180"/>
       <c r="AK50" s="2"/>
       <c r="AL50" s="2"/>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" s="199" t="s">
         <v>668</v>
       </c>
@@ -13204,15 +13416,19 @@
       </c>
       <c r="AI51" s="178" cm="1">
         <f t="array" aca="1" ref="AI51" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V51=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P51))),1,
-IF(V51=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P51))),1,0)),0)</f>
+IF(
+OR(
+V51=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P51)*($AH$2:$AH$282&lt;&gt;0))),
+V51=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P51)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P51)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ51" s="180"/>
       <c r="AK51" s="2"/>
       <c r="AL51" s="2"/>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" s="199" t="s">
         <v>669</v>
       </c>
@@ -13319,15 +13535,19 @@
       </c>
       <c r="AI52" s="178" cm="1">
         <f t="array" aca="1" ref="AI52" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V52=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P52))),1,
-IF(V52=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P52))),1,0)),0)</f>
+IF(
+OR(
+V52=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P52)*($AH$2:$AH$282&lt;&gt;0))),
+V52=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P52)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P52)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ52" s="180"/>
       <c r="AK52" s="2"/>
       <c r="AL52" s="2"/>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" s="199" t="s">
         <v>670</v>
       </c>
@@ -13434,15 +13654,19 @@
       </c>
       <c r="AI53" s="178" cm="1">
         <f t="array" aca="1" ref="AI53" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V53=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P53))),1,
-IF(V53=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P53))),1,0)),0)</f>
+IF(
+OR(
+V53=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P53)*($AH$2:$AH$282&lt;&gt;0))),
+V53=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P53)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P53)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ53" s="180"/>
       <c r="AK53" s="2"/>
       <c r="AL53" s="2"/>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" s="199" t="s">
         <v>671</v>
       </c>
@@ -13549,15 +13773,19 @@
       </c>
       <c r="AI54" s="178" cm="1">
         <f t="array" aca="1" ref="AI54" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V54=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P54))),1,
-IF(V54=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P54))),1,0)),0)</f>
+IF(
+OR(
+V54=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P54)*($AH$2:$AH$282&lt;&gt;0))),
+V54=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P54)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P54)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ54" s="180"/>
       <c r="AK54" s="2"/>
       <c r="AL54" s="2"/>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" s="199" t="s">
         <v>672</v>
       </c>
@@ -13664,15 +13892,19 @@
       </c>
       <c r="AI55" s="178" cm="1">
         <f t="array" aca="1" ref="AI55" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V55=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P55))),1,
-IF(V55=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P55))),1,0)),0)</f>
+IF(
+OR(
+V55=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P55)*($AH$2:$AH$282&lt;&gt;0))),
+V55=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P55)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P55)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ55" s="180"/>
       <c r="AK55" s="2"/>
       <c r="AL55" s="2"/>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" s="199" t="s">
         <v>673</v>
       </c>
@@ -13779,15 +14011,19 @@
       </c>
       <c r="AI56" s="178" cm="1">
         <f t="array" aca="1" ref="AI56" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V56=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P56))),1,
-IF(V56=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P56))),1,0)),0)</f>
+IF(
+OR(
+V56=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P56)*($AH$2:$AH$282&lt;&gt;0))),
+V56=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P56)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P56)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ56" s="180"/>
       <c r="AK56" s="2"/>
       <c r="AL56" s="2"/>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" s="199" t="s">
         <v>674</v>
       </c>
@@ -13894,15 +14130,19 @@
       </c>
       <c r="AI57" s="178" cm="1">
         <f t="array" aca="1" ref="AI57" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V57=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P57))),1,
-IF(V57=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P57))),1,0)),0)</f>
+IF(
+OR(
+V57=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P57)*($AH$2:$AH$282&lt;&gt;0))),
+V57=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P57)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P57)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ57" s="180"/>
       <c r="AK57" s="2"/>
       <c r="AL57" s="2"/>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" s="199" t="s">
         <v>675</v>
       </c>
@@ -14009,15 +14249,19 @@
       </c>
       <c r="AI58" s="178" cm="1">
         <f t="array" aca="1" ref="AI58" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V58=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P58))),1,
-IF(V58=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P58))),1,0)),0)</f>
+IF(
+OR(
+V58=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P58)*($AH$2:$AH$282&lt;&gt;0))),
+V58=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P58)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P58)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ58" s="180"/>
       <c r="AK58" s="2"/>
       <c r="AL58" s="2"/>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" s="199" t="s">
         <v>676</v>
       </c>
@@ -14124,15 +14368,19 @@
       </c>
       <c r="AI59" s="178" cm="1">
         <f t="array" aca="1" ref="AI59" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V59=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P59))),1,
-IF(V59=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P59))),1,0)),0)</f>
+IF(
+OR(
+V59=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P59)*($AH$2:$AH$282&lt;&gt;0))),
+V59=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P59)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P59)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ59" s="180"/>
       <c r="AK59" s="2"/>
       <c r="AL59" s="2"/>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" s="199" t="s">
         <v>677</v>
       </c>
@@ -14239,15 +14487,19 @@
       </c>
       <c r="AI60" s="178" cm="1">
         <f t="array" aca="1" ref="AI60" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V60=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P60))),1,
-IF(V60=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P60))),1,0)),0)</f>
+IF(
+OR(
+V60=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P60)*($AH$2:$AH$282&lt;&gt;0))),
+V60=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P60)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P60)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ60" s="180"/>
       <c r="AK60" s="2"/>
       <c r="AL60" s="2"/>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61" s="199" t="s">
         <v>678</v>
       </c>
@@ -14354,15 +14606,19 @@
       </c>
       <c r="AI61" s="178" cm="1">
         <f t="array" aca="1" ref="AI61" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V61=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P61))),1,
-IF(V61=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P61))),1,0)),0)</f>
+IF(
+OR(
+V61=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P61)*($AH$2:$AH$282&lt;&gt;0))),
+V61=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P61)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P61)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ61" s="180"/>
       <c r="AK61" s="2"/>
       <c r="AL61" s="2"/>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" s="199" t="s">
         <v>679</v>
       </c>
@@ -14469,15 +14725,19 @@
       </c>
       <c r="AI62" s="178" cm="1">
         <f t="array" aca="1" ref="AI62" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V62=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P62))),1,
-IF(V62=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P62))),1,0)),0)</f>
+IF(
+OR(
+V62=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P62)*($AH$2:$AH$282&lt;&gt;0))),
+V62=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P62)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P62)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ62" s="180"/>
       <c r="AK62" s="118"/>
       <c r="AL62" s="2"/>
     </row>
-    <row r="63" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" s="237" t="s">
         <v>704</v>
       </c>
@@ -14568,15 +14828,19 @@
       </c>
       <c r="AI63" s="178" cm="1">
         <f t="array" aca="1" ref="AI63" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V63=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P63))),1,
-IF(V63=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P63))),1,0)),0)</f>
+IF(
+OR(
+V63=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P63)*($AH$2:$AH$282&lt;&gt;0))),
+V63=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P63)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P63)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ63" s="180"/>
       <c r="AK63" s="9"/>
       <c r="AL63" s="9"/>
     </row>
-    <row r="64" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" s="237" t="s">
         <v>705</v>
       </c>
@@ -14667,15 +14931,19 @@
       </c>
       <c r="AI64" s="178" cm="1">
         <f t="array" aca="1" ref="AI64" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V64=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P64))),1,
-IF(V64=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P64))),1,0)),0)</f>
+IF(
+OR(
+V64=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P64)*($AH$2:$AH$282&lt;&gt;0))),
+V64=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P64)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P64)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ64" s="180"/>
       <c r="AK64" s="9"/>
       <c r="AL64" s="9"/>
     </row>
-    <row r="65" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" s="237" t="s">
         <v>706</v>
       </c>
@@ -14766,15 +15034,19 @@
       </c>
       <c r="AI65" s="178" cm="1">
         <f t="array" aca="1" ref="AI65" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V65=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P65))),1,
-IF(V65=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P65))),1,0)),0)</f>
+IF(
+OR(
+V65=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P65)*($AH$2:$AH$282&lt;&gt;0))),
+V65=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P65)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P65)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ65" s="180"/>
       <c r="AK65" s="9"/>
       <c r="AL65" s="9"/>
     </row>
-    <row r="66" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" s="237" t="s">
         <v>707</v>
       </c>
@@ -14865,15 +15137,19 @@
       </c>
       <c r="AI66" s="178" cm="1">
         <f t="array" aca="1" ref="AI66" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V66=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P66))),1,
-IF(V66=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P66))),1,0)),0)</f>
+IF(
+OR(
+V66=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P66)*($AH$2:$AH$282&lt;&gt;0))),
+V66=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P66)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P66)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ66" s="180"/>
       <c r="AK66" s="9"/>
       <c r="AL66" s="9"/>
     </row>
-    <row r="67" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" s="237" t="s">
         <v>708</v>
       </c>
@@ -14964,15 +15240,19 @@
       </c>
       <c r="AI67" s="178" cm="1">
         <f t="array" aca="1" ref="AI67" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V67=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P67))),1,
-IF(V67=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P67))),1,0)),0)</f>
+IF(
+OR(
+V67=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P67)*($AH$2:$AH$282&lt;&gt;0))),
+V67=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P67)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P67)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ67" s="180"/>
       <c r="AK67" s="9"/>
       <c r="AL67" s="9"/>
     </row>
-    <row r="68" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" s="237" t="s">
         <v>709</v>
       </c>
@@ -15063,15 +15343,19 @@
       </c>
       <c r="AI68" s="178" cm="1">
         <f t="array" aca="1" ref="AI68" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V68=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P68))),1,
-IF(V68=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P68))),1,0)),0)</f>
+IF(
+OR(
+V68=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P68)*($AH$2:$AH$282&lt;&gt;0))),
+V68=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P68)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P68)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ68" s="180"/>
       <c r="AK68" s="9"/>
       <c r="AL68" s="9"/>
     </row>
-    <row r="69" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" s="237" t="s">
         <v>710</v>
       </c>
@@ -15162,15 +15446,19 @@
       </c>
       <c r="AI69" s="178" cm="1">
         <f t="array" aca="1" ref="AI69" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V69=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P69))),1,
-IF(V69=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P69))),1,0)),0)</f>
+IF(
+OR(
+V69=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P69)*($AH$2:$AH$282&lt;&gt;0))),
+V69=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P69)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P69)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ69" s="180"/>
       <c r="AK69" s="9"/>
       <c r="AL69" s="9"/>
     </row>
-    <row r="70" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" s="237" t="s">
         <v>711</v>
       </c>
@@ -15261,15 +15549,19 @@
       </c>
       <c r="AI70" s="178" cm="1">
         <f t="array" aca="1" ref="AI70" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V70=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P70))),1,
-IF(V70=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P70))),1,0)),0)</f>
+IF(
+OR(
+V70=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P70)*($AH$2:$AH$282&lt;&gt;0))),
+V70=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P70)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P70)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ70" s="180"/>
       <c r="AK70" s="9"/>
       <c r="AL70" s="9"/>
     </row>
-    <row r="71" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" s="237" t="s">
         <v>701</v>
       </c>
@@ -15356,15 +15648,19 @@
       </c>
       <c r="AI71" s="178" cm="1">
         <f t="array" aca="1" ref="AI71" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V71=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P71))),1,
-IF(V71=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P71))),1,0)),0)</f>
+IF(
+OR(
+V71=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P71)*($AH$2:$AH$282&lt;&gt;0))),
+V71=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P71)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P71)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ71" s="180"/>
       <c r="AK71" s="9"/>
       <c r="AL71" s="9"/>
     </row>
-    <row r="72" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" s="237" t="s">
         <v>702</v>
       </c>
@@ -15455,15 +15751,19 @@
       </c>
       <c r="AI72" s="178" cm="1">
         <f t="array" aca="1" ref="AI72" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V72=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P72))),1,
-IF(V72=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P72))),1,0)),0)</f>
+IF(
+OR(
+V72=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P72)*($AH$2:$AH$282&lt;&gt;0))),
+V72=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P72)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P72)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ72" s="180"/>
       <c r="AK72" s="9"/>
       <c r="AL72" s="9"/>
     </row>
-    <row r="73" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A73" s="237" t="s">
         <v>703</v>
       </c>
@@ -15554,15 +15854,19 @@
       </c>
       <c r="AI73" s="178" cm="1">
         <f t="array" aca="1" ref="AI73" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V73=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P73))),1,
-IF(V73=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P73))),1,0)),0)</f>
+IF(
+OR(
+V73=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P73)*($AH$2:$AH$282&lt;&gt;0))),
+V73=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P73)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P73)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ73" s="180"/>
       <c r="AK73" s="9"/>
       <c r="AL73" s="9"/>
     </row>
-    <row r="74" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" s="237" t="s">
         <v>700</v>
       </c>
@@ -15653,15 +15957,19 @@
       </c>
       <c r="AI74" s="178" cm="1">
         <f t="array" aca="1" ref="AI74" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V74=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P74))),1,
-IF(V74=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P74))),1,0)),0)</f>
+IF(
+OR(
+V74=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P74)*($AH$2:$AH$282&lt;&gt;0))),
+V74=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P74)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P74)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ74" s="180"/>
       <c r="AK74" s="9"/>
       <c r="AL74" s="9"/>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" s="237" t="s">
         <v>472</v>
       </c>
@@ -15752,15 +16060,19 @@
       </c>
       <c r="AI75" s="178" cm="1">
         <f t="array" aca="1" ref="AI75" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V75=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P75))),1,
-IF(V75=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P75))),1,0)),0)</f>
+IF(
+OR(
+V75=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P75)*($AH$2:$AH$282&lt;&gt;0))),
+V75=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P75)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P75)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ75" s="180"/>
       <c r="AK75" s="2"/>
       <c r="AL75" s="2"/>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" s="237" t="s">
         <v>473</v>
       </c>
@@ -15851,15 +16163,19 @@
       </c>
       <c r="AI76" s="178" cm="1">
         <f t="array" aca="1" ref="AI76" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V76=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P76))),1,
-IF(V76=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P76))),1,0)),0)</f>
+IF(
+OR(
+V76=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P76)*($AH$2:$AH$282&lt;&gt;0))),
+V76=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P76)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P76)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ76" s="180"/>
       <c r="AK76" s="2"/>
       <c r="AL76" s="2"/>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" s="237" t="s">
         <v>474</v>
       </c>
@@ -15950,15 +16266,19 @@
       </c>
       <c r="AI77" s="178" cm="1">
         <f t="array" aca="1" ref="AI77" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V77=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P77))),1,
-IF(V77=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P77))),1,0)),0)</f>
+IF(
+OR(
+V77=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P77)*($AH$2:$AH$282&lt;&gt;0))),
+V77=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P77)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P77)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ77" s="180"/>
       <c r="AK77" s="2"/>
       <c r="AL77" s="2"/>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" s="237" t="s">
         <v>475</v>
       </c>
@@ -16049,15 +16369,19 @@
       </c>
       <c r="AI78" s="178" cm="1">
         <f t="array" aca="1" ref="AI78" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V78=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P78))),1,
-IF(V78=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P78))),1,0)),0)</f>
+IF(
+OR(
+V78=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P78)*($AH$2:$AH$282&lt;&gt;0))),
+V78=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P78)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P78)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ78" s="180"/>
       <c r="AK78" s="2"/>
       <c r="AL78" s="2"/>
     </row>
-    <row r="79" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" s="237" t="s">
         <v>476</v>
       </c>
@@ -16148,15 +16472,19 @@
       </c>
       <c r="AI79" s="178" cm="1">
         <f t="array" aca="1" ref="AI79" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V79=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P79))),1,
-IF(V79=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P79))),1,0)),0)</f>
+IF(
+OR(
+V79=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P79)*($AH$2:$AH$282&lt;&gt;0))),
+V79=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P79)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P79)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ79" s="180"/>
       <c r="AK79" s="2"/>
       <c r="AL79" s="2"/>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" s="237" t="s">
         <v>477</v>
       </c>
@@ -16247,15 +16575,19 @@
       </c>
       <c r="AI80" s="178" cm="1">
         <f t="array" aca="1" ref="AI80" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V80=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P80))),1,
-IF(V80=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P80))),1,0)),0)</f>
+IF(
+OR(
+V80=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P80)*($AH$2:$AH$282&lt;&gt;0))),
+V80=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P80)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P80)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ80" s="180"/>
       <c r="AK80" s="2"/>
       <c r="AL80" s="2"/>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" s="359" t="s">
         <v>799</v>
       </c>
@@ -16338,15 +16670,19 @@
       </c>
       <c r="AI81" s="178" cm="1">
         <f t="array" aca="1" ref="AI81" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V81=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P81))),1,
-IF(V81=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P81))),1,0)),0)</f>
+IF(
+OR(
+V81=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P81)*($AH$2:$AH$282&lt;&gt;0))),
+V81=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P81)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P81)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ81" s="180"/>
       <c r="AK81" s="356"/>
       <c r="AL81" s="2"/>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" s="359" t="s">
         <v>800</v>
       </c>
@@ -16429,15 +16765,19 @@
       </c>
       <c r="AI82" s="178" cm="1">
         <f t="array" aca="1" ref="AI82" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V82=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P82))),1,
-IF(V82=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P82))),1,0)),0)</f>
+IF(
+OR(
+V82=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P82)*($AH$2:$AH$282&lt;&gt;0))),
+V82=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P82)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P82)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ82" s="180"/>
       <c r="AK82" s="356"/>
       <c r="AL82" s="2"/>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83" s="359" t="s">
         <v>801</v>
       </c>
@@ -16520,15 +16860,19 @@
       </c>
       <c r="AI83" s="178" cm="1">
         <f t="array" aca="1" ref="AI83" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V83=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P83))),1,
-IF(V83=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P83))),1,0)),0)</f>
+IF(
+OR(
+V83=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P83)*($AH$2:$AH$282&lt;&gt;0))),
+V83=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P83)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P83)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ83" s="180"/>
       <c r="AK83" s="356"/>
       <c r="AL83" s="2"/>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" s="359" t="s">
         <v>802</v>
       </c>
@@ -16611,15 +16955,19 @@
       </c>
       <c r="AI84" s="178" cm="1">
         <f t="array" aca="1" ref="AI84" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V84=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P84))),1,
-IF(V84=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P84))),1,0)),0)</f>
+IF(
+OR(
+V84=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P84)*($AH$2:$AH$282&lt;&gt;0))),
+V84=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P84)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P84)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ84" s="180"/>
       <c r="AK84" s="356"/>
       <c r="AL84" s="2"/>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" s="359" t="s">
         <v>803</v>
       </c>
@@ -16702,15 +17050,19 @@
       </c>
       <c r="AI85" s="178" cm="1">
         <f t="array" aca="1" ref="AI85" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V85=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P85))),1,
-IF(V85=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P85))),1,0)),0)</f>
+IF(
+OR(
+V85=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P85)*($AH$2:$AH$282&lt;&gt;0))),
+V85=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P85)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P85)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ85" s="180"/>
       <c r="AK85" s="356"/>
       <c r="AL85" s="2"/>
     </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" s="359" t="s">
         <v>804</v>
       </c>
@@ -16793,15 +17145,19 @@
       </c>
       <c r="AI86" s="178" cm="1">
         <f t="array" aca="1" ref="AI86" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V86=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P86))),1,
-IF(V86=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P86))),1,0)),0)</f>
+IF(
+OR(
+V86=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P86)*($AH$2:$AH$282&lt;&gt;0))),
+V86=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P86)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P86)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ86" s="180"/>
       <c r="AK86" s="356"/>
       <c r="AL86" s="2"/>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" s="359" t="s">
         <v>805</v>
       </c>
@@ -16884,15 +17240,19 @@
       </c>
       <c r="AI87" s="178" cm="1">
         <f t="array" aca="1" ref="AI87" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V87=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P87))),1,
-IF(V87=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P87))),1,0)),0)</f>
+IF(
+OR(
+V87=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P87)*($AH$2:$AH$282&lt;&gt;0))),
+V87=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P87)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P87)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ87" s="180"/>
       <c r="AK87" s="356"/>
       <c r="AL87" s="2"/>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88" s="359" t="s">
         <v>806</v>
       </c>
@@ -16975,15 +17335,19 @@
       </c>
       <c r="AI88" s="178" cm="1">
         <f t="array" aca="1" ref="AI88" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V88=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P88))),1,
-IF(V88=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P88))),1,0)),0)</f>
+IF(
+OR(
+V88=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P88)*($AH$2:$AH$282&lt;&gt;0))),
+V88=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P88)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P88)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ88" s="180"/>
       <c r="AK88" s="356"/>
       <c r="AL88" s="2"/>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" s="359" t="s">
         <v>807</v>
       </c>
@@ -17066,15 +17430,19 @@
       </c>
       <c r="AI89" s="178" cm="1">
         <f t="array" aca="1" ref="AI89" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V89=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P89))),1,
-IF(V89=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P89))),1,0)),0)</f>
+IF(
+OR(
+V89=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P89)*($AH$2:$AH$282&lt;&gt;0))),
+V89=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P89)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P89)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ89" s="180"/>
       <c r="AK89" s="356"/>
       <c r="AL89" s="2"/>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" s="359" t="s">
         <v>808</v>
       </c>
@@ -17157,15 +17525,19 @@
       </c>
       <c r="AI90" s="178" cm="1">
         <f t="array" aca="1" ref="AI90" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V90=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P90))),1,
-IF(V90=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P90))),1,0)),0)</f>
+IF(
+OR(
+V90=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P90)*($AH$2:$AH$282&lt;&gt;0))),
+V90=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P90)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P90)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ90" s="180"/>
       <c r="AK90" s="356"/>
       <c r="AL90" s="2"/>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" s="359" t="s">
         <v>809</v>
       </c>
@@ -17248,15 +17620,19 @@
       </c>
       <c r="AI91" s="178" cm="1">
         <f t="array" aca="1" ref="AI91" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V91=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P91))),1,
-IF(V91=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P91))),1,0)),0)</f>
+IF(
+OR(
+V91=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P91)*($AH$2:$AH$282&lt;&gt;0))),
+V91=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P91)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P91)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ91" s="180"/>
       <c r="AK91" s="356"/>
       <c r="AL91" s="2"/>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" s="359" t="s">
         <v>810</v>
       </c>
@@ -17339,15 +17715,19 @@
       </c>
       <c r="AI92" s="178" cm="1">
         <f t="array" aca="1" ref="AI92" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V92=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P92))),1,
-IF(V92=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P92))),1,0)),0)</f>
+IF(
+OR(
+V92=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P92)*($AH$2:$AH$282&lt;&gt;0))),
+V92=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P92)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P92)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ92" s="180"/>
       <c r="AK92" s="356"/>
       <c r="AL92" s="2"/>
     </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" s="359" t="s">
         <v>811</v>
       </c>
@@ -17430,15 +17810,19 @@
       </c>
       <c r="AI93" s="178" cm="1">
         <f t="array" aca="1" ref="AI93" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V93=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P93))),1,
-IF(V93=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P93))),1,0)),0)</f>
+IF(
+OR(
+V93=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P93)*($AH$2:$AH$282&lt;&gt;0))),
+V93=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P93)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P93)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ93" s="180"/>
       <c r="AK93" s="356"/>
       <c r="AL93" s="2"/>
     </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" s="359" t="s">
         <v>812</v>
       </c>
@@ -17521,15 +17905,19 @@
       </c>
       <c r="AI94" s="178" cm="1">
         <f t="array" aca="1" ref="AI94" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V94=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P94))),1,
-IF(V94=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P94))),1,0)),0)</f>
+IF(
+OR(
+V94=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P94)*($AH$2:$AH$282&lt;&gt;0))),
+V94=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P94)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P94)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ94" s="180"/>
       <c r="AK94" s="356"/>
       <c r="AL94" s="2"/>
     </row>
-    <row r="95" spans="1:38" s="8" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:38" s="8" customFormat="1" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A95" s="256" t="s">
         <v>193</v>
       </c>
@@ -17620,15 +18008,19 @@
       </c>
       <c r="AI95" s="178" cm="1">
         <f t="array" aca="1" ref="AI95" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V95=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P95))),1,
-IF(V95=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P95))),1,0)),0)</f>
+IF(
+OR(
+V95=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P95)*($AH$2:$AH$282&lt;&gt;0))),
+V95=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P95)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P95)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ95" s="180"/>
       <c r="AK95" s="7"/>
       <c r="AL95" s="7"/>
     </row>
-    <row r="96" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" s="237" t="s">
         <v>191</v>
       </c>
@@ -17718,15 +18110,19 @@
       </c>
       <c r="AI96" s="178" cm="1">
         <f t="array" aca="1" ref="AI96" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V96=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P96))),1,
-IF(V96=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P96))),1,0)),0)</f>
+IF(
+OR(
+V96=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P96)*($AH$2:$AH$282&lt;&gt;0))),
+V96=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P96)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P96)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ96" s="180"/>
       <c r="AK96" s="9"/>
       <c r="AL96" s="9"/>
     </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" s="199" t="s">
         <v>192</v>
       </c>
@@ -17827,15 +18223,19 @@
       </c>
       <c r="AI97" s="178" cm="1">
         <f t="array" aca="1" ref="AI97" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V97=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P97))),1,
-IF(V97=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P97))),1,0)),0)</f>
+IF(
+OR(
+V97=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P97)*($AH$2:$AH$282&lt;&gt;0))),
+V97=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P97)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P97)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ97" s="180"/>
       <c r="AK97" s="2"/>
       <c r="AL97" s="2"/>
     </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" s="199" t="s">
         <v>205</v>
       </c>
@@ -17935,15 +18335,19 @@
       </c>
       <c r="AI98" s="178" cm="1">
         <f t="array" aca="1" ref="AI98" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V98=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P98))),1,
-IF(V98=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P98))),1,0)),0)</f>
+IF(
+OR(
+V98=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P98)*($AH$2:$AH$282&lt;&gt;0))),
+V98=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P98)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P98)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ98" s="180"/>
       <c r="AK98" s="2"/>
       <c r="AL98" s="2"/>
     </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" s="199" t="s">
         <v>201</v>
       </c>
@@ -18044,15 +18448,19 @@
       </c>
       <c r="AI99" s="178" cm="1">
         <f t="array" aca="1" ref="AI99" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V99=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P99))),1,
-IF(V99=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P99))),1,0)),0)</f>
+IF(
+OR(
+V99=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P99)*($AH$2:$AH$282&lt;&gt;0))),
+V99=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P99)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P99)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ99" s="180"/>
       <c r="AK99" s="2"/>
       <c r="AL99" s="2"/>
     </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" s="199" t="s">
         <v>212</v>
       </c>
@@ -18153,8 +18561,12 @@
       </c>
       <c r="AI100" s="178" cm="1">
         <f t="array" aca="1" ref="AI100" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V100=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P100))),1,
-IF(V100=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P100))),1,0)),0)</f>
+IF(
+OR(
+V100=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P100)*($AH$2:$AH$282&lt;&gt;0))),
+V100=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P100)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P100)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ100" s="180"/>
@@ -18163,7 +18575,7 @@
       </c>
       <c r="AL100" s="2"/>
     </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" s="199" t="s">
         <v>202</v>
       </c>
@@ -18263,8 +18675,12 @@
       </c>
       <c r="AI101" s="178" cm="1">
         <f t="array" aca="1" ref="AI101" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V101=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P101))),1,
-IF(V101=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P101))),1,0)),0)</f>
+IF(
+OR(
+V101=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P101)*($AH$2:$AH$282&lt;&gt;0))),
+V101=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P101)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P101)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ101" s="180"/>
@@ -18273,7 +18689,7 @@
       </c>
       <c r="AL101" s="2"/>
     </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" s="199" t="s">
         <v>203</v>
       </c>
@@ -18374,8 +18790,12 @@
       </c>
       <c r="AI102" s="178" cm="1">
         <f t="array" aca="1" ref="AI102" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V102=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P102))),1,
-IF(V102=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P102))),1,0)),0)</f>
+IF(
+OR(
+V102=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P102)*($AH$2:$AH$282&lt;&gt;0))),
+V102=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P102)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P102)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ102" s="180"/>
@@ -18483,15 +18903,19 @@
       </c>
       <c r="AI103" s="178" cm="1">
         <f t="array" aca="1" ref="AI103" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V103=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P103))),1,
-IF(V103=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P103))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V103=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P103)*($AH$2:$AH$282&lt;&gt;0))),
+V103=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P103)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P103)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ103" s="180"/>
       <c r="AK103" s="2"/>
       <c r="AL103" s="2"/>
     </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" s="199" t="s">
         <v>206</v>
       </c>
@@ -18591,15 +19015,19 @@
       </c>
       <c r="AI104" s="178" cm="1">
         <f t="array" aca="1" ref="AI104" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V104=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P104))),1,
-IF(V104=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P104))),1,0)),0)</f>
+IF(
+OR(
+V104=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P104)*($AH$2:$AH$282&lt;&gt;0))),
+V104=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P104)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P104)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ104" s="180"/>
       <c r="AK104" s="2"/>
       <c r="AL104" s="2"/>
     </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" s="199" t="s">
         <v>207</v>
       </c>
@@ -18699,15 +19127,19 @@
       </c>
       <c r="AI105" s="178" cm="1">
         <f t="array" aca="1" ref="AI105" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V105=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P105))),1,
-IF(V105=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P105))),1,0)),0)</f>
+IF(
+OR(
+V105=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P105)*($AH$2:$AH$282&lt;&gt;0))),
+V105=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P105)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P105)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ105" s="180"/>
       <c r="AK105" s="2"/>
       <c r="AL105" s="2"/>
     </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" s="199" t="s">
         <v>208</v>
       </c>
@@ -18807,15 +19239,19 @@
       </c>
       <c r="AI106" s="178" cm="1">
         <f t="array" aca="1" ref="AI106" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V106=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P106))),1,
-IF(V106=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P106))),1,0)),0)</f>
+IF(
+OR(
+V106=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P106)*($AH$2:$AH$282&lt;&gt;0))),
+V106=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P106)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P106)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ106" s="180"/>
       <c r="AK106" s="2"/>
       <c r="AL106" s="2"/>
     </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" s="199" t="s">
         <v>209</v>
       </c>
@@ -18916,15 +19352,19 @@
       </c>
       <c r="AI107" s="178" cm="1">
         <f t="array" aca="1" ref="AI107" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V107=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P107))),1,
-IF(V107=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P107))),1,0)),0)</f>
+IF(
+OR(
+V107=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P107)*($AH$2:$AH$282&lt;&gt;0))),
+V107=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P107)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P107)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ107" s="180"/>
       <c r="AK107" s="2"/>
       <c r="AL107" s="2"/>
     </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" s="199" t="s">
         <v>210</v>
       </c>
@@ -19025,8 +19465,12 @@
       </c>
       <c r="AI108" s="178" cm="1">
         <f t="array" aca="1" ref="AI108" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V108=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P108))),1,
-IF(V108=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P108))),1,0)),0)</f>
+IF(
+OR(
+V108=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P108)*($AH$2:$AH$282&lt;&gt;0))),
+V108=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P108)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P108)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ108" s="180"/>
@@ -19134,15 +19578,19 @@
       </c>
       <c r="AI109" s="178" cm="1">
         <f t="array" aca="1" ref="AI109" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V109=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P109))),1,
-IF(V109=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P109))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V109=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P109)*($AH$2:$AH$282&lt;&gt;0))),
+V109=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P109)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P109)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ109" s="180"/>
       <c r="AK109" s="77"/>
       <c r="AL109" s="77"/>
     </row>
-    <row r="110" spans="1:38" s="78" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:38" s="78" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" s="94" t="s">
         <v>213</v>
       </c>
@@ -19243,15 +19691,19 @@
       </c>
       <c r="AI110" s="178" cm="1">
         <f t="array" aca="1" ref="AI110" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V110=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P110))),1,
-IF(V110=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P110))),1,0)),0)</f>
+IF(
+OR(
+V110=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P110)*($AH$2:$AH$282&lt;&gt;0))),
+V110=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P110)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P110)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ110" s="180"/>
       <c r="AK110" s="77"/>
       <c r="AL110" s="77"/>
     </row>
-    <row r="111" spans="1:38" s="78" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:38" s="78" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" s="94" t="s">
         <v>214</v>
       </c>
@@ -19351,15 +19803,19 @@
       </c>
       <c r="AI111" s="178" cm="1">
         <f t="array" aca="1" ref="AI111" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V111=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P111))),1,
-IF(V111=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P111))),1,0)),0)</f>
+IF(
+OR(
+V111=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P111)*($AH$2:$AH$282&lt;&gt;0))),
+V111=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P111)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P111)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ111" s="180"/>
       <c r="AK111" s="77"/>
       <c r="AL111" s="77"/>
     </row>
-    <row r="112" spans="1:38" s="78" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:38" s="78" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" s="94" t="s">
         <v>211</v>
       </c>
@@ -19459,15 +19915,19 @@
       </c>
       <c r="AI112" s="178" cm="1">
         <f t="array" aca="1" ref="AI112" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V112=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P112))),1,
-IF(V112=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P112))),1,0)),0)</f>
+IF(
+OR(
+V112=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P112)*($AH$2:$AH$282&lt;&gt;0))),
+V112=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P112)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P112)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ112" s="180"/>
       <c r="AK112" s="77"/>
       <c r="AL112" s="77"/>
     </row>
-    <row r="113" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" s="199" t="s">
         <v>216</v>
       </c>
@@ -19567,8 +20027,12 @@
       </c>
       <c r="AI113" s="178" cm="1">
         <f t="array" aca="1" ref="AI113" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V113=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P113))),1,
-IF(V113=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P113))),1,0)),0)</f>
+IF(
+OR(
+V113=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P113)*($AH$2:$AH$282&lt;&gt;0))),
+V113=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P113)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P113)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ113" s="180"/>
@@ -19675,8 +20139,12 @@
       </c>
       <c r="AI114" s="178" cm="1">
         <f t="array" aca="1" ref="AI114" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V114=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P114))),1,
-IF(V114=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P114))),1,0)),0)</f>
+IF(
+OR(
+V114=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P114)*($AH$2:$AH$282&lt;&gt;0))),
+V114=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P114)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P114)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ114" s="180"/>
@@ -19783,8 +20251,12 @@
       </c>
       <c r="AI115" s="178" cm="1">
         <f t="array" aca="1" ref="AI115" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V115=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P115))),1,
-IF(V115=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P115))),1,0)),0)</f>
+IF(
+OR(
+V115=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P115)*($AH$2:$AH$282&lt;&gt;0))),
+V115=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P115)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P115)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ115" s="180"/>
@@ -19893,8 +20365,12 @@
       </c>
       <c r="AI116" s="178" cm="1">
         <f t="array" aca="1" ref="AI116" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V116=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P116))),1,
-IF(V116=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P116))),1,0)),0)</f>
+IF(
+OR(
+V116=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P116)*($AH$2:$AH$282&lt;&gt;0))),
+V116=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P116)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P116)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ116" s="180"/>
@@ -20003,8 +20479,12 @@
       </c>
       <c r="AI117" s="178" cm="1">
         <f t="array" aca="1" ref="AI117" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V117=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P117))),1,
-IF(V117=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P117))),1,0)),0)</f>
+IF(
+OR(
+V117=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P117)*($AH$2:$AH$282&lt;&gt;0))),
+V117=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P117)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P117)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ117" s="180"/>
@@ -20113,8 +20593,12 @@
       </c>
       <c r="AI118" s="178" cm="1">
         <f t="array" aca="1" ref="AI118" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V118=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P118))),1,
-IF(V118=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P118))),1,0)),0)</f>
+IF(
+OR(
+V118=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P118)*($AH$2:$AH$282&lt;&gt;0))),
+V118=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P118)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P118)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ118" s="180"/>
@@ -20223,15 +20707,19 @@
       </c>
       <c r="AI119" s="178" cm="1">
         <f t="array" aca="1" ref="AI119" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V119=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P119))),1,
-IF(V119=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P119))),1,0)),0)</f>
+IF(
+OR(
+V119=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P119)*($AH$2:$AH$282&lt;&gt;0))),
+V119=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P119)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P119)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ119" s="180"/>
       <c r="AK119" s="118"/>
       <c r="AL119" s="2"/>
     </row>
-    <row r="120" spans="1:38" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:38" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A120" s="95" t="s">
         <v>757</v>
       </c>
@@ -20280,15 +20768,19 @@
       </c>
       <c r="AI120" s="178" cm="1">
         <f t="array" aca="1" ref="AI120" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V120=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P120))),1,
-IF(V120=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P120))),1,0)),0)</f>
+IF(
+OR(
+V120=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P120)*($AH$2:$AH$282&lt;&gt;0))),
+V120=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P120)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P120)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ120" s="180"/>
       <c r="AK120" s="3"/>
       <c r="AL120" s="3"/>
     </row>
-    <row r="121" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121" s="167" t="s">
         <v>354</v>
       </c>
@@ -20380,15 +20872,19 @@
       </c>
       <c r="AI121" s="178" cm="1">
         <f t="array" aca="1" ref="AI121" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V121=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P121))),1,
-IF(V121=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P121))),1,0)),0)</f>
+IF(
+OR(
+V121=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P121)*($AH$2:$AH$282&lt;&gt;0))),
+V121=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P121)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P121)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ121" s="180"/>
       <c r="AK121" s="5"/>
       <c r="AL121" s="5"/>
     </row>
-    <row r="122" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122" s="167" t="s">
         <v>355</v>
       </c>
@@ -20480,15 +20976,19 @@
       </c>
       <c r="AI122" s="178" cm="1">
         <f t="array" aca="1" ref="AI122" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V122=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P122))),1,
-IF(V122=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P122))),1,0)),0)</f>
+IF(
+OR(
+V122=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P122)*($AH$2:$AH$282&lt;&gt;0))),
+V122=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P122)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P122)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ122" s="180"/>
       <c r="AK122" s="5"/>
       <c r="AL122" s="5"/>
     </row>
-    <row r="123" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" s="167" t="s">
         <v>356</v>
       </c>
@@ -20580,15 +21080,19 @@
       </c>
       <c r="AI123" s="178" cm="1">
         <f t="array" aca="1" ref="AI123" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V123=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P123))),1,
-IF(V123=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P123))),1,0)),0)</f>
+IF(
+OR(
+V123=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P123)*($AH$2:$AH$282&lt;&gt;0))),
+V123=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P123)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P123)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ123" s="180"/>
       <c r="AK123" s="5"/>
       <c r="AL123" s="5"/>
     </row>
-    <row r="124" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124" s="167" t="s">
         <v>357</v>
       </c>
@@ -20680,15 +21184,19 @@
       </c>
       <c r="AI124" s="178" cm="1">
         <f t="array" aca="1" ref="AI124" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V124=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P124))),1,
-IF(V124=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P124))),1,0)),0)</f>
+IF(
+OR(
+V124=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P124)*($AH$2:$AH$282&lt;&gt;0))),
+V124=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P124)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P124)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ124" s="180"/>
       <c r="AK124" s="5"/>
       <c r="AL124" s="5"/>
     </row>
-    <row r="125" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A125" s="167" t="s">
         <v>358</v>
       </c>
@@ -20780,15 +21288,19 @@
       </c>
       <c r="AI125" s="178" cm="1">
         <f t="array" aca="1" ref="AI125" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V125=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P125))),1,
-IF(V125=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P125))),1,0)),0)</f>
+IF(
+OR(
+V125=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P125)*($AH$2:$AH$282&lt;&gt;0))),
+V125=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P125)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P125)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ125" s="180"/>
       <c r="AK125" s="5"/>
       <c r="AL125" s="5"/>
     </row>
-    <row r="126" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:38" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126" s="167" t="s">
         <v>359</v>
       </c>
@@ -20880,15 +21392,19 @@
       </c>
       <c r="AI126" s="178" cm="1">
         <f t="array" aca="1" ref="AI126" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V126=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P126))),1,
-IF(V126=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P126))),1,0)),0)</f>
+IF(
+OR(
+V126=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P126)*($AH$2:$AH$282&lt;&gt;0))),
+V126=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P126)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P126)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ126" s="180"/>
       <c r="AK126" s="5"/>
       <c r="AL126" s="5"/>
     </row>
-    <row r="127" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127" s="237" t="s">
         <v>369</v>
       </c>
@@ -20979,15 +21495,19 @@
       </c>
       <c r="AI127" s="178" cm="1">
         <f t="array" aca="1" ref="AI127" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V127=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P127))),1,
-IF(V127=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P127))),1,0)),0)</f>
+IF(
+OR(
+V127=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P127)*($AH$2:$AH$282&lt;&gt;0))),
+V127=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P127)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P127)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ127" s="180"/>
       <c r="AK127" s="9"/>
       <c r="AL127" s="9"/>
     </row>
-    <row r="128" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128" s="237" t="s">
         <v>223</v>
       </c>
@@ -21074,15 +21594,19 @@
       </c>
       <c r="AI128" s="178" cm="1">
         <f t="array" aca="1" ref="AI128" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V128=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P128))),1,
-IF(V128=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P128))),1,0)),0)</f>
+IF(
+OR(
+V128=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P128)*($AH$2:$AH$282&lt;&gt;0))),
+V128=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P128)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P128)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ128" s="180"/>
       <c r="AK128" s="9"/>
       <c r="AL128" s="9"/>
     </row>
-    <row r="129" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" s="237" t="s">
         <v>222</v>
       </c>
@@ -21173,15 +21697,19 @@
       </c>
       <c r="AI129" s="178" cm="1">
         <f t="array" aca="1" ref="AI129" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V129=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P129))),1,
-IF(V129=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P129))),1,0)),0)</f>
+IF(
+OR(
+V129=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P129)*($AH$2:$AH$282&lt;&gt;0))),
+V129=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P129)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P129)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ129" s="180"/>
       <c r="AK129" s="9"/>
       <c r="AL129" s="9"/>
     </row>
-    <row r="130" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130" s="237" t="s">
         <v>221</v>
       </c>
@@ -21268,15 +21796,19 @@
       </c>
       <c r="AI130" s="178" cm="1">
         <f t="array" aca="1" ref="AI130" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V130=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P130))),1,
-IF(V130=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P130))),1,0)),0)</f>
+IF(
+OR(
+V130=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P130)*($AH$2:$AH$282&lt;&gt;0))),
+V130=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P130)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P130)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ130" s="180"/>
       <c r="AK130" s="9"/>
       <c r="AL130" s="9"/>
     </row>
-    <row r="131" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" s="237" t="s">
         <v>220</v>
       </c>
@@ -21363,15 +21895,19 @@
       </c>
       <c r="AI131" s="178" cm="1">
         <f t="array" aca="1" ref="AI131" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V131=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P131))),1,
-IF(V131=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P131))),1,0)),0)</f>
+IF(
+OR(
+V131=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P131)*($AH$2:$AH$282&lt;&gt;0))),
+V131=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P131)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P131)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ131" s="180"/>
       <c r="AK131" s="9"/>
       <c r="AL131" s="9"/>
     </row>
-    <row r="132" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132" s="237" t="s">
         <v>830</v>
       </c>
@@ -21450,15 +21986,19 @@
       </c>
       <c r="AI132" s="178" cm="1">
         <f t="array" aca="1" ref="AI132" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V132=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P132))),1,
-IF(V132=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P132))),1,0)),0)</f>
+IF(
+OR(
+V132=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P132)*($AH$2:$AH$282&lt;&gt;0))),
+V132=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P132)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P132)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ132" s="180"/>
       <c r="AK132" s="356"/>
       <c r="AL132" s="2"/>
     </row>
-    <row r="133" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133" s="199" t="s">
         <v>231</v>
       </c>
@@ -21571,8 +22111,12 @@
       </c>
       <c r="AI133" s="178" cm="1">
         <f t="array" aca="1" ref="AI133" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V133=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P133))),1,
-IF(V133=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P133))),1,0)),0)</f>
+IF(
+OR(
+V133=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P133)*($AH$2:$AH$282&lt;&gt;0))),
+V133=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P133)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P133)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ133" s="180"/>
@@ -21581,7 +22125,7 @@
       </c>
       <c r="AL133" s="2"/>
     </row>
-    <row r="134" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134" s="199" t="s">
         <v>231</v>
       </c>
@@ -21694,8 +22238,12 @@
       </c>
       <c r="AI134" s="178" cm="1">
         <f t="array" aca="1" ref="AI134" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V134=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P134))),1,
-IF(V134=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P134))),1,0)),0)</f>
+IF(
+OR(
+V134=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P134)*($AH$2:$AH$282&lt;&gt;0))),
+V134=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P134)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P134)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ134" s="180"/>
@@ -21704,7 +22252,7 @@
       </c>
       <c r="AL134" s="2"/>
     </row>
-    <row r="135" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A135" s="199" t="s">
         <v>231</v>
       </c>
@@ -21817,8 +22365,12 @@
       </c>
       <c r="AI135" s="178" cm="1">
         <f t="array" aca="1" ref="AI135" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V135=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P135))),1,
-IF(V135=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P135))),1,0)),0)</f>
+IF(
+OR(
+V135=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P135)*($AH$2:$AH$282&lt;&gt;0))),
+V135=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P135)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P135)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ135" s="180"/>
@@ -21827,7 +22379,7 @@
       </c>
       <c r="AL135" s="2"/>
     </row>
-    <row r="136" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A136" s="199" t="s">
         <v>230</v>
       </c>
@@ -21942,8 +22494,12 @@
       </c>
       <c r="AI136" s="178" cm="1">
         <f t="array" aca="1" ref="AI136" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V136=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P136))),1,
-IF(V136=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P136))),1,0)),0)</f>
+IF(
+OR(
+V136=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P136)*($AH$2:$AH$282&lt;&gt;0))),
+V136=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P136)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P136)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ136" s="180"/>
@@ -21952,7 +22508,7 @@
       </c>
       <c r="AL136" s="2"/>
     </row>
-    <row r="137" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137" s="199" t="s">
         <v>230</v>
       </c>
@@ -22067,8 +22623,12 @@
       </c>
       <c r="AI137" s="178" cm="1">
         <f t="array" aca="1" ref="AI137" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V137=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P137))),1,
-IF(V137=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P137))),1,0)),0)</f>
+IF(
+OR(
+V137=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P137)*($AH$2:$AH$282&lt;&gt;0))),
+V137=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P137)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P137)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ137" s="180"/>
@@ -22077,7 +22637,7 @@
       </c>
       <c r="AL137" s="2"/>
     </row>
-    <row r="138" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A138" s="199" t="s">
         <v>230</v>
       </c>
@@ -22192,9 +22752,13 @@
       </c>
       <c r="AI138" s="178" cm="1">
         <f t="array" aca="1" ref="AI138" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V138=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P138))),1,
-IF(V138=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P138))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V138=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P138)*($AH$2:$AH$282&lt;&gt;0))),
+V138=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P138)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P138)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ138" s="180"/>
       <c r="AK138" s="2" t="s">
@@ -22202,7 +22766,7 @@
       </c>
       <c r="AL138" s="2"/>
     </row>
-    <row r="139" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A139" s="199" t="s">
         <v>224</v>
       </c>
@@ -22313,15 +22877,19 @@
       </c>
       <c r="AI139" s="178" cm="1">
         <f t="array" aca="1" ref="AI139" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V139=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P139))),1,
-IF(V139=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P139))),1,0)),0)</f>
+IF(
+OR(
+V139=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P139)*($AH$2:$AH$282&lt;&gt;0))),
+V139=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P139)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P139)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ139" s="180"/>
       <c r="AK139" s="2"/>
       <c r="AL139" s="2"/>
     </row>
-    <row r="140" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A140" s="199" t="s">
         <v>225</v>
       </c>
@@ -22436,8 +23004,12 @@
       </c>
       <c r="AI140" s="178" cm="1">
         <f t="array" aca="1" ref="AI140" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V140=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P140))),1,
-IF(V140=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P140))),1,0)),0)</f>
+IF(
+OR(
+V140=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P140)*($AH$2:$AH$282&lt;&gt;0))),
+V140=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P140)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P140)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ140" s="180"/>
@@ -22446,7 +23018,7 @@
       </c>
       <c r="AL140" s="2"/>
     </row>
-    <row r="141" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A141" s="199" t="s">
         <v>225</v>
       </c>
@@ -22561,9 +23133,13 @@
       </c>
       <c r="AI141" s="178" cm="1">
         <f t="array" aca="1" ref="AI141" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V141=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P141))),1,
-IF(V141=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P141))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V141=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P141)*($AH$2:$AH$282&lt;&gt;0))),
+V141=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P141)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P141)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ141" s="180"/>
       <c r="AK141" s="2" t="s">
@@ -22571,7 +23147,7 @@
       </c>
       <c r="AL141" s="2"/>
     </row>
-    <row r="142" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142" s="199" t="s">
         <v>225</v>
       </c>
@@ -22686,8 +23262,12 @@
       </c>
       <c r="AI142" s="178" cm="1">
         <f t="array" aca="1" ref="AI142" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V142=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P142))),1,
-IF(V142=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P142))),1,0)),0)</f>
+IF(
+OR(
+V142=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P142)*($AH$2:$AH$282&lt;&gt;0))),
+V142=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P142)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P142)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ142" s="180"/>
@@ -22696,7 +23276,7 @@
       </c>
       <c r="AL142" s="2"/>
     </row>
-    <row r="143" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143" s="199" t="s">
         <v>262</v>
       </c>
@@ -22811,8 +23391,12 @@
       </c>
       <c r="AI143" s="178" cm="1">
         <f t="array" aca="1" ref="AI143" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V143=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P143))),1,
-IF(V143=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P143))),1,0)),0)</f>
+IF(
+OR(
+V143=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P143)*($AH$2:$AH$282&lt;&gt;0))),
+V143=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P143)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P143)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ143" s="180"/>
@@ -22821,7 +23405,7 @@
       </c>
       <c r="AL143" s="2"/>
     </row>
-    <row r="144" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A144" s="199" t="s">
         <v>262</v>
       </c>
@@ -22936,8 +23520,12 @@
       </c>
       <c r="AI144" s="178" cm="1">
         <f t="array" aca="1" ref="AI144" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V144=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P144))),1,
-IF(V144=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P144))),1,0)),0)</f>
+IF(
+OR(
+V144=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P144)*($AH$2:$AH$282&lt;&gt;0))),
+V144=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P144)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P144)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ144" s="180"/>
@@ -22946,7 +23534,7 @@
       </c>
       <c r="AL144" s="2"/>
     </row>
-    <row r="145" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145" s="199" t="s">
         <v>262</v>
       </c>
@@ -23061,8 +23649,12 @@
       </c>
       <c r="AI145" s="178" cm="1">
         <f t="array" aca="1" ref="AI145" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V145=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P145))),1,
-IF(V145=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P145))),1,0)),0)</f>
+IF(
+OR(
+V145=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P145)*($AH$2:$AH$282&lt;&gt;0))),
+V145=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P145)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P145)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ145" s="180"/>
@@ -23071,7 +23663,7 @@
       </c>
       <c r="AL145" s="2"/>
     </row>
-    <row r="146" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A146" s="199" t="s">
         <v>226</v>
       </c>
@@ -23184,8 +23776,12 @@
       </c>
       <c r="AI146" s="178" cm="1">
         <f t="array" aca="1" ref="AI146" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V146=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P146))),1,
-IF(V146=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P146))),1,0)),0)</f>
+IF(
+OR(
+V146=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P146)*($AH$2:$AH$282&lt;&gt;0))),
+V146=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P146)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P146)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ146" s="180"/>
@@ -23194,7 +23790,7 @@
       </c>
       <c r="AL146" s="2"/>
     </row>
-    <row r="147" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A147" s="199" t="s">
         <v>261</v>
       </c>
@@ -23307,15 +23903,19 @@
       </c>
       <c r="AI147" s="178" cm="1">
         <f t="array" aca="1" ref="AI147" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V147=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P147))),1,
-IF(V147=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P147))),1,0)),0)</f>
+IF(
+OR(
+V147=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P147)*($AH$2:$AH$282&lt;&gt;0))),
+V147=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P147)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P147)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ147" s="180"/>
       <c r="AK147" s="2"/>
       <c r="AL147" s="2"/>
     </row>
-    <row r="148" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A148" s="199" t="s">
         <v>261</v>
       </c>
@@ -23428,15 +24028,19 @@
       </c>
       <c r="AI148" s="178" cm="1">
         <f t="array" aca="1" ref="AI148" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V148=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P148))),1,
-IF(V148=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P148))),1,0)),0)</f>
+IF(
+OR(
+V148=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P148)*($AH$2:$AH$282&lt;&gt;0))),
+V148=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P148)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P148)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ148" s="180"/>
       <c r="AK148" s="2"/>
       <c r="AL148" s="2"/>
     </row>
-    <row r="149" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149" s="199" t="s">
         <v>261</v>
       </c>
@@ -23549,15 +24153,19 @@
       </c>
       <c r="AI149" s="178" cm="1">
         <f t="array" aca="1" ref="AI149" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V149=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P149))),1,
-IF(V149=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P149))),1,0)),0)</f>
+IF(
+OR(
+V149=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P149)*($AH$2:$AH$282&lt;&gt;0))),
+V149=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P149)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P149)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ149" s="180"/>
       <c r="AK149" s="2"/>
       <c r="AL149" s="2"/>
     </row>
-    <row r="150" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" s="199" t="s">
         <v>261</v>
       </c>
@@ -23670,15 +24278,19 @@
       </c>
       <c r="AI150" s="178" cm="1">
         <f t="array" aca="1" ref="AI150" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V150=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P150))),1,
-IF(V150=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P150))),1,0)),0)</f>
+IF(
+OR(
+V150=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P150)*($AH$2:$AH$282&lt;&gt;0))),
+V150=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P150)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P150)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ150" s="180"/>
       <c r="AK150" s="2"/>
       <c r="AL150" s="2"/>
     </row>
-    <row r="151" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:38" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A151" s="199" t="s">
         <v>360</v>
       </c>
@@ -23791,8 +24403,12 @@
       </c>
       <c r="AI151" s="178" cm="1">
         <f t="array" aca="1" ref="AI151" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V151=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P151))),1,
-IF(V151=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P151))),1,0)),0)</f>
+IF(
+OR(
+V151=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P151)*($AH$2:$AH$282&lt;&gt;0))),
+V151=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P151)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P151)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ151" s="180"/>
@@ -23803,7 +24419,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" s="199" t="s">
         <v>227</v>
       </c>
@@ -23916,9 +24532,13 @@
       </c>
       <c r="AI152" s="178" cm="1">
         <f t="array" aca="1" ref="AI152" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V152=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P152))),1,
-IF(V152=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P152))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V152=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P152)*($AH$2:$AH$282&lt;&gt;0))),
+V152=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P152)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P152)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ152" s="180"/>
       <c r="AK152" s="2" t="s">
@@ -23926,7 +24546,7 @@
       </c>
       <c r="AL152" s="2"/>
     </row>
-    <row r="153" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" s="199" t="s">
         <v>228</v>
       </c>
@@ -24039,8 +24659,12 @@
       </c>
       <c r="AI153" s="178" cm="1">
         <f t="array" aca="1" ref="AI153" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V153=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P153))),1,
-IF(V153=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P153))),1,0)),0)</f>
+IF(
+OR(
+V153=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P153)*($AH$2:$AH$282&lt;&gt;0))),
+V153=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P153)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P153)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ153" s="180"/>
@@ -24049,7 +24673,7 @@
       </c>
       <c r="AL153" s="2"/>
     </row>
-    <row r="154" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154" s="199" t="s">
         <v>361</v>
       </c>
@@ -24156,15 +24780,19 @@
       </c>
       <c r="AI154" s="178" cm="1">
         <f t="array" aca="1" ref="AI154" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V154=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P154))),1,
-IF(V154=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P154))),1,0)),0)</f>
+IF(
+OR(
+V154=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P154)*($AH$2:$AH$282&lt;&gt;0))),
+V154=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P154)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P154)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ154" s="180"/>
       <c r="AK154" s="2"/>
       <c r="AL154" s="2"/>
     </row>
-    <row r="155" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155" s="199" t="s">
         <v>229</v>
       </c>
@@ -24277,15 +24905,19 @@
       </c>
       <c r="AI155" s="178" cm="1">
         <f t="array" aca="1" ref="AI155" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V155=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P155))),1,
-IF(V155=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P155))),1,0)),0)</f>
+IF(
+OR(
+V155=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P155)*($AH$2:$AH$282&lt;&gt;0))),
+V155=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P155)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P155)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ155" s="180"/>
       <c r="AK155" s="2"/>
       <c r="AL155" s="2"/>
     </row>
-    <row r="156" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A156" s="199" t="s">
         <v>233</v>
       </c>
@@ -24398,8 +25030,12 @@
       </c>
       <c r="AI156" s="178" cm="1">
         <f t="array" aca="1" ref="AI156" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V156=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P156))),1,
-IF(V156=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P156))),1,0)),0)</f>
+IF(
+OR(
+V156=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P156)*($AH$2:$AH$282&lt;&gt;0))),
+V156=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P156)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P156)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ156" s="180"/>
@@ -24408,7 +25044,7 @@
       </c>
       <c r="AL156" s="2"/>
     </row>
-    <row r="157" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A157" s="199" t="s">
         <v>237</v>
       </c>
@@ -24521,8 +25157,12 @@
       </c>
       <c r="AI157" s="178" cm="1">
         <f t="array" aca="1" ref="AI157" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V157=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P157))),1,
-IF(V157=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P157))),1,0)),0)</f>
+IF(
+OR(
+V157=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P157)*($AH$2:$AH$282&lt;&gt;0))),
+V157=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P157)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P157)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ157" s="180"/>
@@ -24531,7 +25171,7 @@
       </c>
       <c r="AL157" s="2"/>
     </row>
-    <row r="158" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158" s="199" t="s">
         <v>243</v>
       </c>
@@ -24644,8 +25284,12 @@
       </c>
       <c r="AI158" s="178" cm="1">
         <f t="array" aca="1" ref="AI158" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V158=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P158))),1,
-IF(V158=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P158))),1,0)),0)</f>
+IF(
+OR(
+V158=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P158)*($AH$2:$AH$282&lt;&gt;0))),
+V158=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P158)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P158)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ158" s="180"/>
@@ -24656,7 +25300,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="159" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159" s="199" t="s">
         <v>244</v>
       </c>
@@ -24767,15 +25411,19 @@
       </c>
       <c r="AI159" s="178" cm="1">
         <f t="array" aca="1" ref="AI159" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V159=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P159))),1,
-IF(V159=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P159))),1,0)),0)</f>
+IF(
+OR(
+V159=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P159)*($AH$2:$AH$282&lt;&gt;0))),
+V159=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P159)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P159)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ159" s="180"/>
       <c r="AK159" s="2"/>
       <c r="AL159" s="2"/>
     </row>
-    <row r="160" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160" s="199" t="s">
         <v>249</v>
       </c>
@@ -24890,15 +25538,19 @@
       </c>
       <c r="AI160" s="178" cm="1">
         <f t="array" aca="1" ref="AI160" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V160=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P160))),1,
-IF(V160=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P160))),1,0)),0)</f>
+IF(
+OR(
+V160=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P160)*($AH$2:$AH$282&lt;&gt;0))),
+V160=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P160)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P160)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ160" s="180"/>
       <c r="AK160" s="2"/>
       <c r="AL160" s="2"/>
     </row>
-    <row r="161" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161" s="199" t="s">
         <v>249</v>
       </c>
@@ -25013,15 +25665,19 @@
       </c>
       <c r="AI161" s="178" cm="1">
         <f t="array" aca="1" ref="AI161" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V161=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P161))),1,
-IF(V161=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P161))),1,0)),0)</f>
+IF(
+OR(
+V161=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P161)*($AH$2:$AH$282&lt;&gt;0))),
+V161=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P161)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P161)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ161" s="180"/>
       <c r="AK161" s="2"/>
       <c r="AL161" s="2"/>
     </row>
-    <row r="162" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162" s="199" t="s">
         <v>249</v>
       </c>
@@ -25136,15 +25792,19 @@
       </c>
       <c r="AI162" s="178" cm="1">
         <f t="array" aca="1" ref="AI162" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V162=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P162))),1,
-IF(V162=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P162))),1,0)),0)</f>
+IF(
+OR(
+V162=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P162)*($AH$2:$AH$282&lt;&gt;0))),
+V162=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P162)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P162)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ162" s="180"/>
       <c r="AK162" s="2"/>
       <c r="AL162" s="2"/>
     </row>
-    <row r="163" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163" s="199" t="s">
         <v>249</v>
       </c>
@@ -25259,15 +25919,19 @@
       </c>
       <c r="AI163" s="178" cm="1">
         <f t="array" aca="1" ref="AI163" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V163=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P163))),1,
-IF(V163=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P163))),1,0)),0)</f>
+IF(
+OR(
+V163=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P163)*($AH$2:$AH$282&lt;&gt;0))),
+V163=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P163)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P163)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ163" s="180"/>
       <c r="AK163" s="2"/>
       <c r="AL163" s="2"/>
     </row>
-    <row r="164" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A164" s="199" t="s">
         <v>249</v>
       </c>
@@ -25382,15 +26046,19 @@
       </c>
       <c r="AI164" s="178" cm="1">
         <f t="array" aca="1" ref="AI164" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V164=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P164))),1,
-IF(V164=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P164))),1,0)),0)</f>
+IF(
+OR(
+V164=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P164)*($AH$2:$AH$282&lt;&gt;0))),
+V164=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P164)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P164)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ164" s="180"/>
       <c r="AK164" s="2"/>
       <c r="AL164" s="2"/>
     </row>
-    <row r="165" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A165" s="199" t="s">
         <v>249</v>
       </c>
@@ -25505,15 +26173,19 @@
       </c>
       <c r="AI165" s="178" cm="1">
         <f t="array" aca="1" ref="AI165" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V165=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P165))),1,
-IF(V165=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P165))),1,0)),0)</f>
+IF(
+OR(
+V165=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P165)*($AH$2:$AH$282&lt;&gt;0))),
+V165=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P165)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P165)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ165" s="180"/>
       <c r="AK165" s="2"/>
       <c r="AL165" s="2"/>
     </row>
-    <row r="166" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A166" s="199" t="s">
         <v>252</v>
       </c>
@@ -25626,15 +26298,19 @@
       </c>
       <c r="AI166" s="178" cm="1">
         <f t="array" aca="1" ref="AI166" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V166=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P166))),1,
-IF(V166=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P166))),1,0)),0)</f>
+IF(
+OR(
+V166=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P166)*($AH$2:$AH$282&lt;&gt;0))),
+V166=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P166)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P166)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ166" s="180"/>
       <c r="AK166" s="2"/>
       <c r="AL166" s="2"/>
     </row>
-    <row r="167" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A167" s="199" t="s">
         <v>253</v>
       </c>
@@ -25747,15 +26423,19 @@
       </c>
       <c r="AI167" s="178" cm="1">
         <f t="array" aca="1" ref="AI167" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V167=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P167))),1,
-IF(V167=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P167))),1,0)),0)</f>
+IF(
+OR(
+V167=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P167)*($AH$2:$AH$282&lt;&gt;0))),
+V167=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P167)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P167)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ167" s="180"/>
       <c r="AK167" s="2"/>
       <c r="AL167" s="2"/>
     </row>
-    <row r="168" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A168" s="199" t="s">
         <v>253</v>
       </c>
@@ -25868,15 +26548,19 @@
       </c>
       <c r="AI168" s="178" cm="1">
         <f t="array" aca="1" ref="AI168" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V168=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P168))),1,
-IF(V168=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P168))),1,0)),0)</f>
+IF(
+OR(
+V168=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P168)*($AH$2:$AH$282&lt;&gt;0))),
+V168=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P168)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P168)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ168" s="180"/>
       <c r="AK168" s="2"/>
       <c r="AL168" s="2"/>
     </row>
-    <row r="169" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169" s="199" t="s">
         <v>253</v>
       </c>
@@ -25989,15 +26673,19 @@
       </c>
       <c r="AI169" s="178" cm="1">
         <f t="array" aca="1" ref="AI169" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V169=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P169))),1,
-IF(V169=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P169))),1,0)),0)</f>
+IF(
+OR(
+V169=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P169)*($AH$2:$AH$282&lt;&gt;0))),
+V169=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P169)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P169)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ169" s="180"/>
       <c r="AK169" s="2"/>
       <c r="AL169" s="2"/>
     </row>
-    <row r="170" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170" s="199" t="s">
         <v>257</v>
       </c>
@@ -26110,15 +26798,19 @@
       </c>
       <c r="AI170" s="178" cm="1">
         <f t="array" aca="1" ref="AI170" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V170=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P170))),1,
-IF(V170=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P170))),1,0)),0)</f>
+IF(
+OR(
+V170=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P170)*($AH$2:$AH$282&lt;&gt;0))),
+V170=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P170)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P170)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ170" s="180"/>
       <c r="AK170" s="2"/>
       <c r="AL170" s="2"/>
     </row>
-    <row r="171" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171" s="199" t="s">
         <v>258</v>
       </c>
@@ -26229,15 +26921,19 @@
       </c>
       <c r="AI171" s="178" cm="1">
         <f t="array" aca="1" ref="AI171" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V171=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P171))),1,
-IF(V171=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P171))),1,0)),0)</f>
+IF(
+OR(
+V171=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P171)*($AH$2:$AH$282&lt;&gt;0))),
+V171=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P171)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P171)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ171" s="180"/>
       <c r="AK171" s="2"/>
       <c r="AL171" s="2"/>
     </row>
-    <row r="172" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172" s="199" t="s">
         <v>263</v>
       </c>
@@ -26348,15 +27044,19 @@
       </c>
       <c r="AI172" s="178" cm="1">
         <f t="array" aca="1" ref="AI172" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V172=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P172))),1,
-IF(V172=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P172))),1,0)),0)</f>
+IF(
+OR(
+V172=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P172)*($AH$2:$AH$282&lt;&gt;0))),
+V172=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P172)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P172)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ172" s="180"/>
       <c r="AK172" s="2"/>
       <c r="AL172" s="2"/>
     </row>
-    <row r="173" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173" s="199" t="s">
         <v>268</v>
       </c>
@@ -26469,9 +27169,13 @@
       </c>
       <c r="AI173" s="178" cm="1">
         <f t="array" aca="1" ref="AI173" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V173=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P173))),1,
-IF(V173=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P173))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V173=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P173)*($AH$2:$AH$282&lt;&gt;0))),
+V173=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P173)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P173)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ173" s="180"/>
       <c r="AK173" s="2" t="s">
@@ -26479,7 +27183,7 @@
       </c>
       <c r="AL173" s="2"/>
     </row>
-    <row r="174" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A174" s="199" t="s">
         <v>270</v>
       </c>
@@ -26583,8 +27287,12 @@
       </c>
       <c r="AI174" s="178" cm="1">
         <f t="array" aca="1" ref="AI174" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V174=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P174))),1,
-IF(V174=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P174))),1,0)),0)</f>
+IF(
+OR(
+V174=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P174)*($AH$2:$AH$282&lt;&gt;0))),
+V174=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P174)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P174)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ174" s="180"/>
@@ -26593,7 +27301,7 @@
       </c>
       <c r="AL174" s="2"/>
     </row>
-    <row r="175" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A175" s="199" t="s">
         <v>271</v>
       </c>
@@ -26706,8 +27414,12 @@
       </c>
       <c r="AI175" s="178" cm="1">
         <f t="array" aca="1" ref="AI175" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V175=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P175))),1,
-IF(V175=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P175))),1,0)),0)</f>
+IF(
+OR(
+V175=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P175)*($AH$2:$AH$282&lt;&gt;0))),
+V175=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P175)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P175)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ175" s="180"/>
@@ -26716,7 +27428,7 @@
       </c>
       <c r="AL175" s="2"/>
     </row>
-    <row r="176" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A176" s="199" t="s">
         <v>271</v>
       </c>
@@ -26829,8 +27541,12 @@
       </c>
       <c r="AI176" s="178" cm="1">
         <f t="array" aca="1" ref="AI176" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V176=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P176))),1,
-IF(V176=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P176))),1,0)),0)</f>
+IF(
+OR(
+V176=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P176)*($AH$2:$AH$282&lt;&gt;0))),
+V176=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P176)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P176)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ176" s="180"/>
@@ -26839,7 +27555,7 @@
       </c>
       <c r="AL176" s="2"/>
     </row>
-    <row r="177" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A177" s="199" t="s">
         <v>271</v>
       </c>
@@ -26952,8 +27668,12 @@
       </c>
       <c r="AI177" s="178" cm="1">
         <f t="array" aca="1" ref="AI177" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V177=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P177))),1,
-IF(V177=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P177))),1,0)),0)</f>
+IF(
+OR(
+V177=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P177)*($AH$2:$AH$282&lt;&gt;0))),
+V177=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P177)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P177)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ177" s="180"/>
@@ -26962,7 +27682,7 @@
       </c>
       <c r="AL177" s="2"/>
     </row>
-    <row r="178" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178" s="199" t="s">
         <v>275</v>
       </c>
@@ -27075,8 +27795,12 @@
       </c>
       <c r="AI178" s="178" cm="1">
         <f t="array" aca="1" ref="AI178" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V178=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P178))),1,
-IF(V178=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P178))),1,0)),0)</f>
+IF(
+OR(
+V178=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P178)*($AH$2:$AH$282&lt;&gt;0))),
+V178=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P178)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P178)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ178" s="180"/>
@@ -27087,7 +27811,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="179" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179" s="199" t="s">
         <v>278</v>
       </c>
@@ -27200,8 +27924,12 @@
       </c>
       <c r="AI179" s="178" cm="1">
         <f t="array" aca="1" ref="AI179" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V179=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P179))),1,
-IF(V179=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P179))),1,0)),0)</f>
+IF(
+OR(
+V179=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P179)*($AH$2:$AH$282&lt;&gt;0))),
+V179=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P179)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P179)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ179" s="180"/>
@@ -27210,7 +27938,7 @@
       </c>
       <c r="AL179" s="2"/>
     </row>
-    <row r="180" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A180" s="199" t="s">
         <v>282</v>
       </c>
@@ -27323,15 +28051,19 @@
       </c>
       <c r="AI180" s="178" cm="1">
         <f t="array" aca="1" ref="AI180" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V180=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P180))),1,
-IF(V180=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P180))),1,0)),0)</f>
+IF(
+OR(
+V180=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P180)*($AH$2:$AH$282&lt;&gt;0))),
+V180=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P180)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P180)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ180" s="180"/>
       <c r="AK180" s="2"/>
       <c r="AL180" s="2"/>
     </row>
-    <row r="181" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181" s="199" t="s">
         <v>282</v>
       </c>
@@ -27444,15 +28176,19 @@
       </c>
       <c r="AI181" s="178" cm="1">
         <f t="array" aca="1" ref="AI181" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V181=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P181))),1,
-IF(V181=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P181))),1,0)),0)</f>
+IF(
+OR(
+V181=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P181)*($AH$2:$AH$282&lt;&gt;0))),
+V181=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P181)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P181)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ181" s="180"/>
       <c r="AK181" s="2"/>
       <c r="AL181" s="2"/>
     </row>
-    <row r="182" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182" s="199" t="s">
         <v>282</v>
       </c>
@@ -27565,15 +28301,19 @@
       </c>
       <c r="AI182" s="178" cm="1">
         <f t="array" aca="1" ref="AI182" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V182=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P182))),1,
-IF(V182=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P182))),1,0)),0)</f>
+IF(
+OR(
+V182=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P182)*($AH$2:$AH$282&lt;&gt;0))),
+V182=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P182)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P182)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ182" s="180"/>
       <c r="AK182" s="2"/>
       <c r="AL182" s="2"/>
     </row>
-    <row r="183" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A183" s="199" t="s">
         <v>286</v>
       </c>
@@ -27686,15 +28426,19 @@
       </c>
       <c r="AI183" s="178" cm="1">
         <f t="array" aca="1" ref="AI183" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V183=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P183))),1,
-IF(V183=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P183))),1,0)),0)</f>
+IF(
+OR(
+V183=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P183)*($AH$2:$AH$282&lt;&gt;0))),
+V183=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P183)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P183)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ183" s="180"/>
       <c r="AK183" s="2"/>
       <c r="AL183" s="2"/>
     </row>
-    <row r="184" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A184" s="199" t="s">
         <v>292</v>
       </c>
@@ -27807,8 +28551,12 @@
       </c>
       <c r="AI184" s="178" cm="1">
         <f t="array" aca="1" ref="AI184" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V184=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P184))),1,
-IF(V184=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P184))),1,0)),0)</f>
+IF(
+OR(
+V184=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P184)*($AH$2:$AH$282&lt;&gt;0))),
+V184=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P184)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P184)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ184" s="180"/>
@@ -27817,7 +28565,7 @@
       </c>
       <c r="AL184" s="2"/>
     </row>
-    <row r="185" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A185" s="199" t="s">
         <v>298</v>
       </c>
@@ -27930,8 +28678,12 @@
       </c>
       <c r="AI185" s="178" cm="1">
         <f t="array" aca="1" ref="AI185" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V185=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P185))),1,
-IF(V185=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P185))),1,0)),0)</f>
+IF(
+OR(
+V185=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P185)*($AH$2:$AH$282&lt;&gt;0))),
+V185=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P185)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P185)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ185" s="180"/>
@@ -27940,7 +28692,7 @@
       </c>
       <c r="AL185" s="2"/>
     </row>
-    <row r="186" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A186" s="199" t="s">
         <v>302</v>
       </c>
@@ -28053,8 +28805,12 @@
       </c>
       <c r="AI186" s="178" cm="1">
         <f t="array" aca="1" ref="AI186" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V186=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P186))),1,
-IF(V186=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P186))),1,0)),0)</f>
+IF(
+OR(
+V186=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P186)*($AH$2:$AH$282&lt;&gt;0))),
+V186=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P186)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P186)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ186" s="180"/>
@@ -28063,7 +28819,7 @@
       </c>
       <c r="AL186" s="2"/>
     </row>
-    <row r="187" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187" s="199" t="s">
         <v>303</v>
       </c>
@@ -28176,8 +28932,12 @@
       </c>
       <c r="AI187" s="178" cm="1">
         <f t="array" aca="1" ref="AI187" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V187=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P187))),1,
-IF(V187=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P187))),1,0)),0)</f>
+IF(
+OR(
+V187=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P187)*($AH$2:$AH$282&lt;&gt;0))),
+V187=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P187)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P187)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ187" s="180"/>
@@ -28186,7 +28946,7 @@
       </c>
       <c r="AL187" s="2"/>
     </row>
-    <row r="188" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A188" s="199" t="s">
         <v>307</v>
       </c>
@@ -28299,8 +29059,12 @@
       </c>
       <c r="AI188" s="178" cm="1">
         <f t="array" aca="1" ref="AI188" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V188=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P188))),1,
-IF(V188=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P188))),1,0)),0)</f>
+IF(
+OR(
+V188=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P188)*($AH$2:$AH$282&lt;&gt;0))),
+V188=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P188)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P188)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ188" s="180"/>
@@ -28309,7 +29073,7 @@
       </c>
       <c r="AL188" s="2"/>
     </row>
-    <row r="189" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A189" s="199" t="s">
         <v>309</v>
       </c>
@@ -28422,8 +29186,12 @@
       </c>
       <c r="AI189" s="178" cm="1">
         <f t="array" aca="1" ref="AI189" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V189=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P189))),1,
-IF(V189=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P189))),1,0)),0)</f>
+IF(
+OR(
+V189=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P189)*($AH$2:$AH$282&lt;&gt;0))),
+V189=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P189)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P189)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ189" s="180"/>
@@ -28434,7 +29202,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="190" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190" s="199" t="s">
         <v>310</v>
       </c>
@@ -28547,9 +29315,13 @@
       </c>
       <c r="AI190" s="178" cm="1">
         <f t="array" aca="1" ref="AI190" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V190=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P190))),1,
-IF(V190=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P190))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V190=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P190)*($AH$2:$AH$282&lt;&gt;0))),
+V190=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P190)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P190)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ190" s="180"/>
       <c r="AK190" s="2" t="s">
@@ -28559,7 +29331,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="191" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A191" s="199" t="s">
         <v>453</v>
       </c>
@@ -28672,8 +29444,12 @@
       </c>
       <c r="AI191" s="178" cm="1">
         <f t="array" aca="1" ref="AI191" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V191=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P191))),1,
-IF(V191=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P191))),1,0)),0)</f>
+IF(
+OR(
+V191=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P191)*($AH$2:$AH$282&lt;&gt;0))),
+V191=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P191)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P191)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ191" s="180"/>
@@ -28682,7 +29458,7 @@
       </c>
       <c r="AL191" s="2"/>
     </row>
-    <row r="192" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A192" s="155" t="s">
         <v>564</v>
       </c>
@@ -28795,15 +29571,19 @@
       </c>
       <c r="AI192" s="178" cm="1">
         <f t="array" aca="1" ref="AI192" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V192=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P192))),1,
-IF(V192=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P192))),1,0)),0)</f>
+IF(
+OR(
+V192=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P192)*($AH$2:$AH$282&lt;&gt;0))),
+V192=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P192)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P192)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ192" s="180"/>
       <c r="AK192" s="118"/>
       <c r="AL192" s="2"/>
     </row>
-    <row r="193" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A193" s="155" t="s">
         <v>565</v>
       </c>
@@ -28916,15 +29696,19 @@
       </c>
       <c r="AI193" s="178" cm="1">
         <f t="array" aca="1" ref="AI193" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V193=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P193))),1,
-IF(V193=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P193))),1,0)),0)</f>
+IF(
+OR(
+V193=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P193)*($AH$2:$AH$282&lt;&gt;0))),
+V193=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P193)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P193)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ193" s="180"/>
       <c r="AK193" s="118"/>
       <c r="AL193" s="2"/>
     </row>
-    <row r="194" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A194" s="155" t="s">
         <v>565</v>
       </c>
@@ -29037,15 +29821,19 @@
       </c>
       <c r="AI194" s="178" cm="1">
         <f t="array" aca="1" ref="AI194" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V194=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P194))),1,
-IF(V194=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P194))),1,0)),0)</f>
+IF(
+OR(
+V194=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P194)*($AH$2:$AH$282&lt;&gt;0))),
+V194=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P194)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P194)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ194" s="180"/>
       <c r="AK194" s="118"/>
       <c r="AL194" s="2"/>
     </row>
-    <row r="195" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A195" s="155" t="s">
         <v>572</v>
       </c>
@@ -29134,15 +29922,19 @@
       </c>
       <c r="AI195" s="178" cm="1">
         <f t="array" aca="1" ref="AI195" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V195=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P195))),1,
-IF(V195=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P195))),1,0)),0)</f>
+IF(
+OR(
+V195=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P195)*($AH$2:$AH$282&lt;&gt;0))),
+V195=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P195)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P195)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ195" s="180"/>
       <c r="AK195" s="118"/>
       <c r="AL195" s="2"/>
     </row>
-    <row r="196" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A196" s="155" t="s">
         <v>577</v>
       </c>
@@ -29258,15 +30050,19 @@
       </c>
       <c r="AI196" s="178" cm="1">
         <f t="array" aca="1" ref="AI196" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V196=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P196))),1,
-IF(V196=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P196))),1,0)),0)</f>
+IF(
+OR(
+V196=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P196)*($AH$2:$AH$282&lt;&gt;0))),
+V196=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P196)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P196)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ196" s="180"/>
       <c r="AK196" s="118"/>
       <c r="AL196" s="2"/>
     </row>
-    <row r="197" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197" s="155" t="s">
         <v>577</v>
       </c>
@@ -29382,15 +30178,19 @@
       </c>
       <c r="AI197" s="178" cm="1">
         <f t="array" aca="1" ref="AI197" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V197=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P197))),1,
-IF(V197=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P197))),1,0)),0)</f>
+IF(
+OR(
+V197=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P197)*($AH$2:$AH$282&lt;&gt;0))),
+V197=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P197)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P197)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ197" s="180"/>
       <c r="AK197" s="118"/>
       <c r="AL197" s="2"/>
     </row>
-    <row r="198" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A198" s="199" t="s">
         <v>578</v>
       </c>
@@ -29503,15 +30303,19 @@
       </c>
       <c r="AI198" s="178" cm="1">
         <f t="array" aca="1" ref="AI198" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V198=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P198))),1,
-IF(V198=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P198))),1,0)),0)</f>
+IF(
+OR(
+V198=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P198)*($AH$2:$AH$282&lt;&gt;0))),
+V198=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P198)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P198)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ198" s="180"/>
       <c r="AK198" s="118"/>
       <c r="AL198" s="2"/>
     </row>
-    <row r="199" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A199" s="199" t="s">
         <v>583</v>
       </c>
@@ -29624,15 +30428,19 @@
       </c>
       <c r="AI199" s="178" cm="1">
         <f t="array" aca="1" ref="AI199" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V199=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P199))),1,
-IF(V199=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P199))),1,0)),0)</f>
+IF(
+OR(
+V199=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P199)*($AH$2:$AH$282&lt;&gt;0))),
+V199=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P199)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P199)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ199" s="180"/>
       <c r="AK199" s="118"/>
       <c r="AL199" s="2"/>
     </row>
-    <row r="200" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200" s="199" t="s">
         <v>586</v>
       </c>
@@ -29747,15 +30555,19 @@
       </c>
       <c r="AI200" s="178" cm="1">
         <f t="array" aca="1" ref="AI200" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V200=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P200))),1,
-IF(V200=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P200))),1,0)),0)</f>
+IF(
+OR(
+V200=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P200)*($AH$2:$AH$282&lt;&gt;0))),
+V200=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P200)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P200)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ200" s="180"/>
       <c r="AK200" s="2"/>
       <c r="AL200" s="2"/>
     </row>
-    <row r="201" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A201" s="199" t="s">
         <v>586</v>
       </c>
@@ -29870,15 +30682,19 @@
       </c>
       <c r="AI201" s="178" cm="1">
         <f t="array" aca="1" ref="AI201" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V201=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P201))),1,
-IF(V201=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P201))),1,0)),0)</f>
+IF(
+OR(
+V201=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P201)*($AH$2:$AH$282&lt;&gt;0))),
+V201=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P201)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P201)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ201" s="180"/>
       <c r="AK201" s="2"/>
       <c r="AL201" s="2"/>
     </row>
-    <row r="202" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202" s="199" t="s">
         <v>586</v>
       </c>
@@ -29993,15 +30809,19 @@
       </c>
       <c r="AI202" s="178" cm="1">
         <f t="array" aca="1" ref="AI202" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V202=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P202))),1,
-IF(V202=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P202))),1,0)),0)</f>
+IF(
+OR(
+V202=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P202)*($AH$2:$AH$282&lt;&gt;0))),
+V202=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P202)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P202)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ202" s="180"/>
       <c r="AK202" s="2"/>
       <c r="AL202" s="2"/>
     </row>
-    <row r="203" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203" s="199" t="s">
         <v>586</v>
       </c>
@@ -30116,15 +30936,19 @@
       </c>
       <c r="AI203" s="178" cm="1">
         <f t="array" aca="1" ref="AI203" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V203=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P203))),1,
-IF(V203=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P203))),1,0)),0)</f>
+IF(
+OR(
+V203=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P203)*($AH$2:$AH$282&lt;&gt;0))),
+V203=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P203)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P203)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ203" s="180"/>
       <c r="AK203" s="2"/>
       <c r="AL203" s="2"/>
     </row>
-    <row r="204" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204" s="199" t="s">
         <v>589</v>
       </c>
@@ -30237,15 +31061,19 @@
       </c>
       <c r="AI204" s="178" cm="1">
         <f t="array" aca="1" ref="AI204" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V204=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P204))),1,
-IF(V204=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P204))),1,0)),0)</f>
+IF(
+OR(
+V204=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P204)*($AH$2:$AH$282&lt;&gt;0))),
+V204=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P204)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P204)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ204" s="180"/>
       <c r="AK204" s="2"/>
       <c r="AL204" s="2"/>
     </row>
-    <row r="205" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205" s="199" t="s">
         <v>592</v>
       </c>
@@ -30360,15 +31188,19 @@
       </c>
       <c r="AI205" s="178" cm="1">
         <f t="array" aca="1" ref="AI205" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V205=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P205))),1,
-IF(V205=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P205))),1,0)),0)</f>
+IF(
+OR(
+V205=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P205)*($AH$2:$AH$282&lt;&gt;0))),
+V205=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P205)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P205)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ205" s="180"/>
       <c r="AK205" s="118"/>
       <c r="AL205" s="2"/>
     </row>
-    <row r="206" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206" s="199" t="s">
         <v>592</v>
       </c>
@@ -30483,15 +31315,19 @@
       </c>
       <c r="AI206" s="178" cm="1">
         <f t="array" aca="1" ref="AI206" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V206=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P206))),1,
-IF(V206=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P206))),1,0)),0)</f>
+IF(
+OR(
+V206=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P206)*($AH$2:$AH$282&lt;&gt;0))),
+V206=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P206)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P206)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ206" s="180"/>
       <c r="AK206" s="2"/>
       <c r="AL206" s="2"/>
     </row>
-    <row r="207" spans="1:38" s="165" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:38" s="165" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207" s="199" t="s">
         <v>596</v>
       </c>
@@ -30604,15 +31440,19 @@
       </c>
       <c r="AI207" s="178" cm="1">
         <f t="array" aca="1" ref="AI207" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V207=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P207))),1,
-IF(V207=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P207))),1,0)),0)</f>
+IF(
+OR(
+V207=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P207)*($AH$2:$AH$282&lt;&gt;0))),
+V207=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P207)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P207)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ207" s="180"/>
       <c r="AK207" s="2"/>
       <c r="AL207" s="2"/>
     </row>
-    <row r="208" spans="1:38" s="165" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:38" s="165" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208" s="155" t="s">
         <v>774</v>
       </c>
@@ -30726,15 +31566,19 @@
       </c>
       <c r="AI208" s="178" cm="1">
         <f t="array" aca="1" ref="AI208" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V208=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P208))),1,
-IF(V208=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P208))),1,0)),0)</f>
+IF(
+OR(
+V208=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P208)*($AH$2:$AH$282&lt;&gt;0))),
+V208=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P208)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P208)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ208" s="180"/>
       <c r="AK208" s="118"/>
       <c r="AL208" s="2"/>
     </row>
-    <row r="209" spans="1:38" s="165" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:38" s="165" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209" s="155" t="s">
         <v>775</v>
       </c>
@@ -30850,15 +31694,19 @@
       </c>
       <c r="AI209" s="178" cm="1">
         <f t="array" aca="1" ref="AI209" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V209=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P209))),1,
-IF(V209=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P209))),1,0)),0)</f>
+IF(
+OR(
+V209=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P209)*($AH$2:$AH$282&lt;&gt;0))),
+V209=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P209)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P209)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ209" s="180"/>
       <c r="AK209" s="118"/>
       <c r="AL209" s="2"/>
     </row>
-    <row r="210" spans="1:38" s="165" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:38" s="165" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A210" s="155" t="s">
         <v>775</v>
       </c>
@@ -30974,15 +31822,19 @@
       </c>
       <c r="AI210" s="178" cm="1">
         <f t="array" aca="1" ref="AI210" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V210=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P210))),1,
-IF(V210=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P210))),1,0)),0)</f>
+IF(
+OR(
+V210=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P210)*($AH$2:$AH$282&lt;&gt;0))),
+V210=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P210)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P210)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ210" s="180"/>
       <c r="AK210" s="118"/>
       <c r="AL210" s="2"/>
     </row>
-    <row r="211" spans="1:38" s="145" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:38" s="145" customFormat="1" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A211" s="129" t="s">
         <v>775</v>
       </c>
@@ -31098,15 +31950,19 @@
       </c>
       <c r="AI211" s="178" cm="1">
         <f t="array" aca="1" ref="AI211" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V211=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P211))),1,
-IF(V211=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P211))),1,0)),0)</f>
+IF(
+OR(
+V211=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P211)*($AH$2:$AH$282&lt;&gt;0))),
+V211=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P211)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P211)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ211" s="180"/>
       <c r="AK211" s="166"/>
       <c r="AL211" s="3"/>
     </row>
-    <row r="212" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A212" s="237" t="s">
         <v>362</v>
       </c>
@@ -31195,15 +32051,19 @@
       </c>
       <c r="AI212" s="178" cm="1">
         <f t="array" aca="1" ref="AI212" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V212=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P212))),1,
-IF(V212=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P212))),1,0)),0)</f>
+IF(
+OR(
+V212=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P212)*($AH$2:$AH$282&lt;&gt;0))),
+V212=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P212)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P212)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ212" s="180"/>
       <c r="AK212" s="59"/>
       <c r="AL212" s="59"/>
     </row>
-    <row r="213" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A213" s="199" t="s">
         <v>363</v>
       </c>
@@ -31304,15 +32164,19 @@
       </c>
       <c r="AI213" s="178" cm="1">
         <f t="array" aca="1" ref="AI213" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V213=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P213))),1,
-IF(V213=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P213))),1,0)),0)</f>
+IF(
+OR(
+V213=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P213)*($AH$2:$AH$282&lt;&gt;0))),
+V213=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P213)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P213)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ213" s="180"/>
       <c r="AK213" s="60"/>
       <c r="AL213" s="60"/>
     </row>
-    <row r="214" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A214" s="199" t="s">
         <v>363</v>
       </c>
@@ -31413,15 +32277,19 @@
       </c>
       <c r="AI214" s="178" cm="1">
         <f t="array" aca="1" ref="AI214" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V214=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P214))),1,
-IF(V214=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P214))),1,0)),0)</f>
+IF(
+OR(
+V214=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P214)*($AH$2:$AH$282&lt;&gt;0))),
+V214=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P214)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P214)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ214" s="180"/>
       <c r="AK214" s="60"/>
       <c r="AL214" s="60"/>
     </row>
-    <row r="215" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215" s="199" t="s">
         <v>363</v>
       </c>
@@ -31522,15 +32390,19 @@
       </c>
       <c r="AI215" s="178" cm="1">
         <f t="array" aca="1" ref="AI215" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V215=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P215))),1,
-IF(V215=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P215))),1,0)),0)</f>
+IF(
+OR(
+V215=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P215)*($AH$2:$AH$282&lt;&gt;0))),
+V215=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P215)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P215)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ215" s="180"/>
       <c r="AK215" s="60"/>
       <c r="AL215" s="60"/>
     </row>
-    <row r="216" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A216" s="199" t="s">
         <v>363</v>
       </c>
@@ -31631,15 +32503,19 @@
       </c>
       <c r="AI216" s="178" cm="1">
         <f t="array" aca="1" ref="AI216" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V216=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P216))),1,
-IF(V216=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P216))),1,0)),0)</f>
+IF(
+OR(
+V216=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P216)*($AH$2:$AH$282&lt;&gt;0))),
+V216=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P216)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P216)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ216" s="180"/>
       <c r="AK216" s="60"/>
       <c r="AL216" s="60"/>
     </row>
-    <row r="217" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A217" s="199" t="s">
         <v>364</v>
       </c>
@@ -31739,15 +32615,19 @@
       </c>
       <c r="AI217" s="178" cm="1">
         <f t="array" aca="1" ref="AI217" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V217=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P217))),1,
-IF(V217=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P217))),1,0)),0)</f>
+IF(
+OR(
+V217=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P217)*($AH$2:$AH$282&lt;&gt;0))),
+V217=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P217)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P217)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ217" s="180"/>
       <c r="AK217" s="60"/>
       <c r="AL217" s="60"/>
     </row>
-    <row r="218" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A218" s="199" t="s">
         <v>365</v>
       </c>
@@ -31849,15 +32729,19 @@
       </c>
       <c r="AI218" s="178" cm="1">
         <f t="array" aca="1" ref="AI218" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V218=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P218))),1,
-IF(V218=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P218))),1,0)),0)</f>
+IF(
+OR(
+V218=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P218)*($AH$2:$AH$282&lt;&gt;0))),
+V218=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P218)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P218)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ218" s="180"/>
       <c r="AK218" s="60"/>
       <c r="AL218" s="60"/>
     </row>
-    <row r="219" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219" s="199" t="s">
         <v>365</v>
       </c>
@@ -31959,15 +32843,19 @@
       </c>
       <c r="AI219" s="178" cm="1">
         <f t="array" aca="1" ref="AI219" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V219=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P219))),1,
-IF(V219=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P219))),1,0)),0)</f>
+IF(
+OR(
+V219=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P219)*($AH$2:$AH$282&lt;&gt;0))),
+V219=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P219)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P219)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ219" s="180"/>
       <c r="AK219" s="60"/>
       <c r="AL219" s="60"/>
     </row>
-    <row r="220" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220" s="199" t="s">
         <v>365</v>
       </c>
@@ -32069,15 +32957,19 @@
       </c>
       <c r="AI220" s="178" cm="1">
         <f t="array" aca="1" ref="AI220" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V220=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P220))),1,
-IF(V220=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P220))),1,0)),0)</f>
+IF(
+OR(
+V220=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P220)*($AH$2:$AH$282&lt;&gt;0))),
+V220=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P220)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P220)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ220" s="180"/>
       <c r="AK220" s="60"/>
       <c r="AL220" s="60"/>
     </row>
-    <row r="221" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221" s="199" t="s">
         <v>366</v>
       </c>
@@ -32177,15 +33069,19 @@
       </c>
       <c r="AI221" s="178" cm="1">
         <f t="array" aca="1" ref="AI221" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V221=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P221))),1,
-IF(V221=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P221))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V221=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P221)*($AH$2:$AH$282&lt;&gt;0))),
+V221=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P221)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P221)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ221" s="180"/>
       <c r="AK221" s="60"/>
       <c r="AL221" s="60"/>
     </row>
-    <row r="222" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A222" s="199" t="s">
         <v>367</v>
       </c>
@@ -32287,15 +33183,19 @@
       </c>
       <c r="AI222" s="178" cm="1">
         <f t="array" aca="1" ref="AI222" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V222=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P222))),1,
-IF(V222=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P222))),1,0)),0)</f>
+IF(
+OR(
+V222=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P222)*($AH$2:$AH$282&lt;&gt;0))),
+V222=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P222)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P222)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ222" s="180"/>
       <c r="AK222" s="60"/>
       <c r="AL222" s="60"/>
     </row>
-    <row r="223" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223" s="199" t="s">
         <v>367</v>
       </c>
@@ -32397,15 +33297,19 @@
       </c>
       <c r="AI223" s="178" cm="1">
         <f t="array" aca="1" ref="AI223" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V223=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P223))),1,
-IF(V223=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P223))),1,0)),0)</f>
+IF(
+OR(
+V223=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P223)*($AH$2:$AH$282&lt;&gt;0))),
+V223=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P223)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P223)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ223" s="180"/>
       <c r="AK223" s="60"/>
       <c r="AL223" s="60"/>
     </row>
-    <row r="224" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224" s="199" t="s">
         <v>367</v>
       </c>
@@ -32507,15 +33411,19 @@
       </c>
       <c r="AI224" s="178" cm="1">
         <f t="array" aca="1" ref="AI224" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V224=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P224))),1,
-IF(V224=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P224))),1,0)),0)</f>
+IF(
+OR(
+V224=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P224)*($AH$2:$AH$282&lt;&gt;0))),
+V224=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P224)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P224)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ224" s="180"/>
       <c r="AK224" s="60"/>
       <c r="AL224" s="60"/>
     </row>
-    <row r="225" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225" s="199" t="s">
         <v>367</v>
       </c>
@@ -32617,15 +33525,19 @@
       </c>
       <c r="AI225" s="178" cm="1">
         <f t="array" aca="1" ref="AI225" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V225=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P225))),1,
-IF(V225=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P225))),1,0)),0)</f>
+IF(
+OR(
+V225=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P225)*($AH$2:$AH$282&lt;&gt;0))),
+V225=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P225)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P225)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ225" s="180"/>
       <c r="AK225" s="60"/>
       <c r="AL225" s="60"/>
     </row>
-    <row r="226" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226" s="199" t="s">
         <v>368</v>
       </c>
@@ -32726,15 +33638,19 @@
       </c>
       <c r="AI226" s="178" cm="1">
         <f t="array" aca="1" ref="AI226" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V226=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P226))),1,
-IF(V226=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P226))),1,0)),0)</f>
+IF(
+OR(
+V226=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P226)*($AH$2:$AH$282&lt;&gt;0))),
+V226=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P226)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P226)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ226" s="180"/>
       <c r="AK226" s="60"/>
       <c r="AL226" s="60"/>
     </row>
-    <row r="227" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A227" s="199" t="s">
         <v>368</v>
       </c>
@@ -32835,15 +33751,19 @@
       </c>
       <c r="AI227" s="178" cm="1">
         <f t="array" aca="1" ref="AI227" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V227=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P227))),1,
-IF(V227=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P227))),1,0)),0)</f>
+IF(
+OR(
+V227=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P227)*($AH$2:$AH$282&lt;&gt;0))),
+V227=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P227)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P227)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ227" s="180"/>
       <c r="AK227" s="60"/>
       <c r="AL227" s="60"/>
     </row>
-    <row r="228" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228" s="199" t="s">
         <v>368</v>
       </c>
@@ -32944,15 +33864,19 @@
       </c>
       <c r="AI228" s="178" cm="1">
         <f t="array" aca="1" ref="AI228" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V228=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P228))),1,
-IF(V228=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P228))),1,0)),0)</f>
+IF(
+OR(
+V228=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P228)*($AH$2:$AH$282&lt;&gt;0))),
+V228=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P228)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P228)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ228" s="180"/>
       <c r="AK228" s="60"/>
       <c r="AL228" s="60"/>
     </row>
-    <row r="229" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:38" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229" s="94" t="s">
         <v>368</v>
       </c>
@@ -33053,15 +33977,19 @@
       </c>
       <c r="AI229" s="178" cm="1">
         <f t="array" aca="1" ref="AI229" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V229=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P229))),1,
-IF(V229=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P229))),1,0)),0)</f>
+IF(
+OR(
+V229=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P229)*($AH$2:$AH$282&lt;&gt;0))),
+V229=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P229)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P229)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ229" s="180"/>
       <c r="AK229" s="60"/>
       <c r="AL229" s="60"/>
     </row>
-    <row r="230" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230" s="94" t="s">
         <v>430</v>
       </c>
@@ -33164,8 +34092,12 @@
       </c>
       <c r="AI230" s="178" cm="1">
         <f t="array" aca="1" ref="AI230" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V230=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P230))),1,
-IF(V230=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P230))),1,0)),0)</f>
+IF(
+OR(
+V230=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P230)*($AH$2:$AH$282&lt;&gt;0))),
+V230=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P230)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P230)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ230" s="180"/>
@@ -33174,7 +34106,7 @@
       </c>
       <c r="AL230" s="2"/>
     </row>
-    <row r="231" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A231" s="94" t="s">
         <v>430</v>
       </c>
@@ -33277,8 +34209,12 @@
       </c>
       <c r="AI231" s="178" cm="1">
         <f t="array" aca="1" ref="AI231" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V231=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P231))),1,
-IF(V231=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P231))),1,0)),0)</f>
+IF(
+OR(
+V231=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P231)*($AH$2:$AH$282&lt;&gt;0))),
+V231=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P231)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P231)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ231" s="180"/>
@@ -33287,7 +34223,7 @@
       </c>
       <c r="AL231" s="2"/>
     </row>
-    <row r="232" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A232" s="94" t="s">
         <v>434</v>
       </c>
@@ -33388,15 +34324,19 @@
       </c>
       <c r="AI232" s="178" cm="1">
         <f t="array" aca="1" ref="AI232" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V232=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P232))),1,
-IF(V232=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P232))),1,0)),0)</f>
+IF(
+OR(
+V232=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P232)*($AH$2:$AH$282&lt;&gt;0))),
+V232=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P232)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P232)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ232" s="180"/>
       <c r="AK232" s="60"/>
       <c r="AL232" s="60"/>
     </row>
-    <row r="233" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A233" s="94" t="s">
         <v>434</v>
       </c>
@@ -33497,15 +34437,19 @@
       </c>
       <c r="AI233" s="178" cm="1">
         <f t="array" aca="1" ref="AI233" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V233=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P233))),1,
-IF(V233=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P233))),1,0)),0)</f>
+IF(
+OR(
+V233=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P233)*($AH$2:$AH$282&lt;&gt;0))),
+V233=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P233)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P233)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ233" s="180"/>
       <c r="AK233" s="60"/>
       <c r="AL233" s="60"/>
     </row>
-    <row r="234" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A234" s="94" t="s">
         <v>434</v>
       </c>
@@ -33606,15 +34550,19 @@
       </c>
       <c r="AI234" s="178" cm="1">
         <f t="array" aca="1" ref="AI234" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V234=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P234))),1,
-IF(V234=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P234))),1,0)),0)</f>
+IF(
+OR(
+V234=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P234)*($AH$2:$AH$282&lt;&gt;0))),
+V234=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P234)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P234)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ234" s="180"/>
       <c r="AK234" s="60"/>
       <c r="AL234" s="60"/>
     </row>
-    <row r="235" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A235" s="94" t="s">
         <v>434</v>
       </c>
@@ -33715,15 +34663,19 @@
       </c>
       <c r="AI235" s="178" cm="1">
         <f t="array" aca="1" ref="AI235" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V235=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P235))),1,
-IF(V235=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P235))),1,0)),0)</f>
+IF(
+OR(
+V235=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P235)*($AH$2:$AH$282&lt;&gt;0))),
+V235=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P235)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P235)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ235" s="180"/>
       <c r="AK235" s="60"/>
       <c r="AL235" s="60"/>
     </row>
-    <row r="236" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A236" s="94" t="s">
         <v>437</v>
       </c>
@@ -33824,8 +34776,12 @@
       </c>
       <c r="AI236" s="178" cm="1">
         <f t="array" aca="1" ref="AI236" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V236=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P236))),1,
-IF(V236=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P236))),1,0)),0)</f>
+IF(
+OR(
+V236=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P236)*($AH$2:$AH$282&lt;&gt;0))),
+V236=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P236)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P236)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ236" s="180"/>
@@ -33834,7 +34790,7 @@
       </c>
       <c r="AL236" s="2"/>
     </row>
-    <row r="237" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A237" s="94" t="s">
         <v>437</v>
       </c>
@@ -33935,8 +34891,12 @@
       </c>
       <c r="AI237" s="178" cm="1">
         <f t="array" aca="1" ref="AI237" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V237=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P237))),1,
-IF(V237=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P237))),1,0)),0)</f>
+IF(
+OR(
+V237=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P237)*($AH$2:$AH$282&lt;&gt;0))),
+V237=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P237)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P237)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ237" s="180"/>
@@ -33945,7 +34905,7 @@
       </c>
       <c r="AL237" s="2"/>
     </row>
-    <row r="238" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A238" s="94" t="s">
         <v>437</v>
       </c>
@@ -34046,8 +35006,12 @@
       </c>
       <c r="AI238" s="178" cm="1">
         <f t="array" aca="1" ref="AI238" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V238=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P238))),1,
-IF(V238=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P238))),1,0)),0)</f>
+IF(
+OR(
+V238=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P238)*($AH$2:$AH$282&lt;&gt;0))),
+V238=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P238)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P238)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ238" s="180"/>
@@ -34056,7 +35020,7 @@
       </c>
       <c r="AL238" s="2"/>
     </row>
-    <row r="239" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239" s="94" t="s">
         <v>438</v>
       </c>
@@ -34159,8 +35123,12 @@
       </c>
       <c r="AI239" s="178" cm="1">
         <f t="array" aca="1" ref="AI239" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V239=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P239))),1,
-IF(V239=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P239))),1,0)),0)</f>
+IF(
+OR(
+V239=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P239)*($AH$2:$AH$282&lt;&gt;0))),
+V239=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P239)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P239)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ239" s="180"/>
@@ -34169,7 +35137,7 @@
       </c>
       <c r="AL239" s="2"/>
     </row>
-    <row r="240" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A240" s="94" t="s">
         <v>438</v>
       </c>
@@ -34272,8 +35240,12 @@
       </c>
       <c r="AI240" s="178" cm="1">
         <f t="array" aca="1" ref="AI240" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V240=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P240))),1,
-IF(V240=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P240))),1,0)),0)</f>
+IF(
+OR(
+V240=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P240)*($AH$2:$AH$282&lt;&gt;0))),
+V240=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P240)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P240)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ240" s="180"/>
@@ -34282,7 +35254,7 @@
       </c>
       <c r="AL240" s="2"/>
     </row>
-    <row r="241" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A241" s="94" t="s">
         <v>438</v>
       </c>
@@ -34385,8 +35357,12 @@
       </c>
       <c r="AI241" s="178" cm="1">
         <f t="array" aca="1" ref="AI241" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V241=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P241))),1,
-IF(V241=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P241))),1,0)),0)</f>
+IF(
+OR(
+V241=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P241)*($AH$2:$AH$282&lt;&gt;0))),
+V241=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P241)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P241)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ241" s="180"/>
@@ -34395,7 +35371,7 @@
       </c>
       <c r="AL241" s="2"/>
     </row>
-    <row r="242" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242" s="94" t="s">
         <v>439</v>
       </c>
@@ -34495,15 +35471,19 @@
       </c>
       <c r="AI242" s="178" cm="1">
         <f t="array" aca="1" ref="AI242" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V242=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P242))),1,
-IF(V242=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P242))),1,0)),0)</f>
+IF(
+OR(
+V242=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P242)*($AH$2:$AH$282&lt;&gt;0))),
+V242=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P242)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P242)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ242" s="180"/>
       <c r="AK242" s="2"/>
       <c r="AL242" s="2"/>
     </row>
-    <row r="243" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243" s="94" t="s">
         <v>443</v>
       </c>
@@ -34605,15 +35585,19 @@
       </c>
       <c r="AI243" s="178" cm="1">
         <f t="array" aca="1" ref="AI243" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V243=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P243))),1,
-IF(V243=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P243))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V243=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P243)*($AH$2:$AH$282&lt;&gt;0))),
+V243=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P243)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P243)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ243" s="180"/>
       <c r="AK243" s="2"/>
       <c r="AL243" s="2"/>
     </row>
-    <row r="244" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A244" s="94" t="s">
         <v>443</v>
       </c>
@@ -34715,15 +35699,19 @@
       </c>
       <c r="AI244" s="178" cm="1">
         <f t="array" aca="1" ref="AI244" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V244=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P244))),1,
-IF(V244=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P244))),1,0)),0)</f>
+IF(
+OR(
+V244=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P244)*($AH$2:$AH$282&lt;&gt;0))),
+V244=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P244)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P244)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ244" s="180"/>
       <c r="AK244" s="2"/>
       <c r="AL244" s="2"/>
     </row>
-    <row r="245" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245" s="94" t="s">
         <v>443</v>
       </c>
@@ -34825,15 +35813,19 @@
       </c>
       <c r="AI245" s="178" cm="1">
         <f t="array" aca="1" ref="AI245" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V245=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P245))),1,
-IF(V245=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P245))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V245=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P245)*($AH$2:$AH$282&lt;&gt;0))),
+V245=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P245)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P245)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ245" s="180"/>
       <c r="AK245" s="2"/>
       <c r="AL245" s="2"/>
     </row>
-    <row r="246" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A246" s="94" t="s">
         <v>444</v>
       </c>
@@ -34933,8 +35925,12 @@
       </c>
       <c r="AI246" s="178" cm="1">
         <f t="array" aca="1" ref="AI246" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V246=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P246))),1,
-IF(V246=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P246))),1,0)),0)</f>
+IF(
+OR(
+V246=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P246)*($AH$2:$AH$282&lt;&gt;0))),
+V246=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P246)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P246)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ246" s="180"/>
@@ -34943,7 +35939,7 @@
       </c>
       <c r="AL246" s="2"/>
     </row>
-    <row r="247" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A247" s="94" t="s">
         <v>445</v>
       </c>
@@ -35043,8 +36039,12 @@
       </c>
       <c r="AI247" s="178" cm="1">
         <f t="array" aca="1" ref="AI247" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V247=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P247))),1,
-IF(V247=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P247))),1,0)),0)</f>
+IF(
+OR(
+V247=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P247)*($AH$2:$AH$282&lt;&gt;0))),
+V247=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P247)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P247)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ247" s="180"/>
@@ -35053,7 +36053,7 @@
       </c>
       <c r="AL247" s="80"/>
     </row>
-    <row r="248" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248" s="94" t="s">
         <v>446</v>
       </c>
@@ -35155,15 +36155,19 @@
       </c>
       <c r="AI248" s="178" cm="1">
         <f t="array" aca="1" ref="AI248" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V248=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P248))),1,
-IF(V248=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P248))),1,0)),0)</f>
+IF(
+OR(
+V248=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P248)*($AH$2:$AH$282&lt;&gt;0))),
+V248=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P248)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P248)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ248" s="180"/>
       <c r="AK248" s="103"/>
       <c r="AL248" s="2"/>
     </row>
-    <row r="249" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A249" s="94" t="s">
         <v>446</v>
       </c>
@@ -35265,15 +36269,19 @@
       </c>
       <c r="AI249" s="178" cm="1">
         <f t="array" aca="1" ref="AI249" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V249=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P249))),1,
-IF(V249=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P249))),1,0)),0)</f>
+IF(
+OR(
+V249=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P249)*($AH$2:$AH$282&lt;&gt;0))),
+V249=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P249)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P249)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ249" s="180"/>
       <c r="AK249" s="2"/>
       <c r="AL249" s="2"/>
     </row>
-    <row r="250" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250" s="94" t="s">
         <v>461</v>
       </c>
@@ -35375,15 +36383,19 @@
       </c>
       <c r="AI250" s="178" cm="1">
         <f t="array" aca="1" ref="AI250" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V250=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P250))),1,
-IF(V250=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P250))),1,0)),0)</f>
+IF(
+OR(
+V250=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P250)*($AH$2:$AH$282&lt;&gt;0))),
+V250=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P250)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P250)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ250" s="180"/>
       <c r="AK250" s="2"/>
       <c r="AL250" s="2"/>
     </row>
-    <row r="251" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251" s="94" t="s">
         <v>461</v>
       </c>
@@ -35485,15 +36497,19 @@
       </c>
       <c r="AI251" s="178" cm="1">
         <f t="array" aca="1" ref="AI251" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V251=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P251))),1,
-IF(V251=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P251))),1,0)),0)</f>
+IF(
+OR(
+V251=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P251)*($AH$2:$AH$282&lt;&gt;0))),
+V251=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P251)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P251)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ251" s="180"/>
       <c r="AK251" s="2"/>
       <c r="AL251" s="2"/>
     </row>
-    <row r="252" spans="1:38" s="144" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:38" s="144" customFormat="1" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A252" s="129" t="s">
         <v>464</v>
       </c>
@@ -35594,15 +36610,19 @@
       </c>
       <c r="AI252" s="178" cm="1">
         <f t="array" aca="1" ref="AI252" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V252=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P252))),1,
-IF(V252=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P252))),1,0)),0)</f>
+IF(
+OR(
+V252=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P252)*($AH$2:$AH$282&lt;&gt;0))),
+V252=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P252)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P252)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ252" s="180"/>
       <c r="AK252" s="131"/>
       <c r="AL252" s="143"/>
     </row>
-    <row r="253" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A253" s="94" t="s">
         <v>174</v>
       </c>
@@ -35699,8 +36719,12 @@
       </c>
       <c r="AI253" s="178" cm="1">
         <f t="array" aca="1" ref="AI253" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V253=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P253))),1,
-IF(V253=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P253))),1,0)),0)</f>
+IF(
+OR(
+V253=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P253)*($AH$2:$AH$282&lt;&gt;0))),
+V253=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P253)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P253)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ253" s="180"/>
@@ -35709,7 +36733,7 @@
       </c>
       <c r="AL253" s="2"/>
     </row>
-    <row r="254" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254" s="199" t="s">
         <v>175</v>
       </c>
@@ -35806,15 +36830,19 @@
       </c>
       <c r="AI254" s="178" cm="1">
         <f t="array" aca="1" ref="AI254" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V254=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P254))),1,
-IF(V254=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P254))),1,0)),0)</f>
+IF(
+OR(
+V254=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P254)*($AH$2:$AH$282&lt;&gt;0))),
+V254=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P254)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P254)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ254" s="180"/>
       <c r="AK254" s="2"/>
       <c r="AL254" s="2"/>
     </row>
-    <row r="255" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255" s="199" t="s">
         <v>176</v>
       </c>
@@ -35913,8 +36941,12 @@
       </c>
       <c r="AI255" s="178" cm="1">
         <f t="array" aca="1" ref="AI255" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V255=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P255))),1,
-IF(V255=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P255))),1,0)),0)</f>
+IF(
+OR(
+V255=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P255)*($AH$2:$AH$282&lt;&gt;0))),
+V255=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P255)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P255)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ255" s="180"/>
@@ -35923,7 +36955,7 @@
       </c>
       <c r="AL255" s="2"/>
     </row>
-    <row r="256" spans="1:38" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:38" hidden="1" x14ac:dyDescent="0.45">
       <c r="A256" s="199" t="s">
         <v>176</v>
       </c>
@@ -36022,8 +37054,12 @@
       </c>
       <c r="AI256" s="178" cm="1">
         <f t="array" aca="1" ref="AI256" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V256=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P256))),1,
-IF(V256=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P256))),1,0)),0)</f>
+IF(
+OR(
+V256=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P256)*($AH$2:$AH$282&lt;&gt;0))),
+V256=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P256)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P256)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ256" s="180"/>
@@ -36032,7 +37068,7 @@
       </c>
       <c r="AL256" s="2"/>
     </row>
-    <row r="257" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:39" hidden="1" x14ac:dyDescent="0.45">
       <c r="A257" s="199" t="s">
         <v>177</v>
       </c>
@@ -36132,9 +37168,13 @@
       </c>
       <c r="AI257" s="178" cm="1">
         <f t="array" aca="1" ref="AI257" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V257=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P257))),1,
-IF(V257=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P257))),1,0)),0)</f>
-        <v>0</v>
+IF(
+OR(
+V257=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P257)*($AH$2:$AH$282&lt;&gt;0))),
+V257=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P257)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P257)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
+        <v>1</v>
       </c>
       <c r="AJ257" s="180"/>
       <c r="AK257" s="2" t="s">
@@ -36142,7 +37182,7 @@
       </c>
       <c r="AL257" s="2"/>
     </row>
-    <row r="258" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:39" hidden="1" x14ac:dyDescent="0.45">
       <c r="A258" s="199" t="s">
         <v>177</v>
       </c>
@@ -36242,8 +37282,12 @@
       </c>
       <c r="AI258" s="178" cm="1">
         <f t="array" aca="1" ref="AI258" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V258=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P258))),1,
-IF(V258=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P258))),1,0)),0)</f>
+IF(
+OR(
+V258=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P258)*($AH$2:$AH$282&lt;&gt;0))),
+V258=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P258)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P258)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ258" s="180"/>
@@ -36252,7 +37296,7 @@
       </c>
       <c r="AL258" s="2"/>
     </row>
-    <row r="259" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:39" hidden="1" x14ac:dyDescent="0.45">
       <c r="A259" s="199" t="s">
         <v>178</v>
       </c>
@@ -36350,15 +37394,19 @@
       </c>
       <c r="AI259" s="178" cm="1">
         <f t="array" aca="1" ref="AI259" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V259=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P259))),1,
-IF(V259=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P259))),1,0)),0)</f>
+IF(
+OR(
+V259=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P259)*($AH$2:$AH$282&lt;&gt;0))),
+V259=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P259)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P259)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ259" s="180"/>
       <c r="AK259" s="2"/>
       <c r="AL259" s="2"/>
     </row>
-    <row r="260" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:39" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260" s="199" t="s">
         <v>179</v>
       </c>
@@ -36456,15 +37504,19 @@
       </c>
       <c r="AI260" s="178" cm="1">
         <f t="array" aca="1" ref="AI260" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V260=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P260))),1,
-IF(V260=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P260))),1,0)),0)</f>
+IF(
+OR(
+V260=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P260)*($AH$2:$AH$282&lt;&gt;0))),
+V260=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P260)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P260)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ260" s="180"/>
       <c r="AK260" s="2"/>
       <c r="AL260" s="2"/>
     </row>
-    <row r="261" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:39" hidden="1" x14ac:dyDescent="0.45">
       <c r="A261" s="199" t="s">
         <v>180</v>
       </c>
@@ -36561,15 +37613,19 @@
       </c>
       <c r="AI261" s="178" cm="1">
         <f t="array" aca="1" ref="AI261" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V261=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P261))),1,
-IF(V261=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P261))),1,0)),0)</f>
+IF(
+OR(
+V261=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P261)*($AH$2:$AH$282&lt;&gt;0))),
+V261=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P261)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P261)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ261" s="180"/>
       <c r="AK261" s="2"/>
       <c r="AL261" s="2"/>
     </row>
-    <row r="262" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:39" hidden="1" x14ac:dyDescent="0.45">
       <c r="A262" s="199" t="s">
         <v>181</v>
       </c>
@@ -36666,15 +37722,19 @@
       </c>
       <c r="AI262" s="178" cm="1">
         <f t="array" aca="1" ref="AI262" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V262=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P262))),1,
-IF(V262=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P262))),1,0)),0)</f>
+IF(
+OR(
+V262=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P262)*($AH$2:$AH$282&lt;&gt;0))),
+V262=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P262)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P262)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ262" s="180"/>
       <c r="AK262" s="2"/>
       <c r="AL262" s="2"/>
     </row>
-    <row r="263" spans="1:39" s="144" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:39" s="144" customFormat="1" ht="14.65" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A263" s="129" t="s">
         <v>182</v>
       </c>
@@ -36771,15 +37831,19 @@
       </c>
       <c r="AI263" s="178" cm="1">
         <f t="array" aca="1" ref="AI263" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V263=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P263))),1,
-IF(V263=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P263))),1,0)),0)</f>
+IF(
+OR(
+V263=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P263)*($AH$2:$AH$282&lt;&gt;0))),
+V263=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P263)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P263)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>1</v>
       </c>
       <c r="AJ263" s="180"/>
       <c r="AK263" s="131"/>
       <c r="AL263" s="143"/>
     </row>
-    <row r="264" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:39" hidden="1" x14ac:dyDescent="0.45">
       <c r="A264" s="199" t="s">
         <v>183</v>
       </c>
@@ -36871,8 +37935,12 @@
       </c>
       <c r="AI264" s="178" cm="1">
         <f t="array" aca="1" ref="AI264" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V264=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P264))),1,
-IF(V264=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P264))),1,0)),0)</f>
+IF(
+OR(
+V264=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P264)*($AH$2:$AH$282&lt;&gt;0))),
+V264=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P264)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P264)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ264" s="180"/>
@@ -36881,7 +37949,7 @@
       </c>
       <c r="AL264" s="2"/>
     </row>
-    <row r="265" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:39" hidden="1" x14ac:dyDescent="0.45">
       <c r="A265" s="199" t="s">
         <v>184</v>
       </c>
@@ -36973,8 +38041,12 @@
       </c>
       <c r="AI265" s="178" cm="1">
         <f t="array" aca="1" ref="AI265" ca="1">IF(Table24[[#This Row],[gültig]]&lt;&gt;0,
-IF(V265=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P265))),1,
-IF(V265=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P265))),1,0)),0)</f>
+IF(
+OR(
+V265=MIN(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P265)*($AH$2:$AH$282&lt;&gt;0))),
+V265=MAX(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P265)*($AH$2:$AH$282&lt;&gt;0))),
+ROWS(_xlfn._xlws.FILTER($V$2:$V$282,($P$2:$P$282=P265)*($AH$2:$AH$282&lt;&gt;0)))&lt;=2
+),1,0),0)</f>
         <v>0</v>
       </c>
       <c r="AJ265" s="180"/>

--- a/Database/260506_Datenbankdefinition_Hochbau.xlsx
+++ b/Database/260506_Datenbankdefinition_Hochbau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodelan\PycharmProjects\StustainabilityDrivenStructuralDesign\260513_Betonartikel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F06B84C-D90D-4935-9451-0137B9A17AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5EDC21-88C2-4263-A361-C0D156CCD57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-8850" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="43080" yWindow="-8850" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="clarification" sheetId="5" r:id="rId1"/>
@@ -39880,7 +39880,7 @@
       <c r="E6" s="23"/>
       <c r="F6" s="23"/>
       <c r="G6" s="365">
-        <v>205000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>

--- a/Database/260506_Datenbankdefinition_Hochbau.xlsx
+++ b/Database/260506_Datenbankdefinition_Hochbau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hodelan\PycharmProjects\StustainabilityDrivenStructuralDesign\260513_Betonartikel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5EDC21-88C2-4263-A361-C0D156CCD57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CEAC507-BCD1-4B64-8B98-5BDCAE69EFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-8850" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{58B6788A-438B-478E-898A-D53025B55ED1}"/>
   </bookViews>
   <sheets>
     <sheet name="clarification" sheetId="5" r:id="rId1"/>
@@ -40400,11 +40400,11 @@
         <v>6</v>
       </c>
       <c r="F5" s="23">
-        <v>2000</v>
+        <v>1450</v>
       </c>
       <c r="G5" s="23">
         <f t="shared" si="0"/>
-        <v>20000</v>
+        <v>14500</v>
       </c>
       <c r="H5" s="23">
         <v>1.7999999999999999E-2</v>
